--- a/results/evaluation/semantic_candidates.xlsx
+++ b/results/evaluation/semantic_candidates.xlsx
@@ -7376,7 +7376,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7388,16 +7388,16 @@
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>18703</v>
+        <v>13674</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Thần Bí Khôi Phục: Nếu [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Đồng Nhân, Huyền Nghi, Linh Dị</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -7406,11 +7406,11 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.4294</v>
+        <v>0.4339</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18703-than-bi-khoi-phuc-neu-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7434,29 +7434,29 @@
         <v>2</v>
       </c>
       <c r="E153" t="n">
-        <v>20773</v>
+        <v>2818</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Công tử đẹp trai quá [Dịch]</t>
+          <t>Nghịch Thiên Tà Thần [Convert]</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.4194</v>
+        <v>0.3906</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20773-cong-tu-dep-trai-qua-dich</t>
+          <t>https://sitruyencv.com/story/2818-nghich-thien-ta-than-convert</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7480,16 +7480,16 @@
         <v>3</v>
       </c>
       <c r="E154" t="n">
-        <v>20799</v>
+        <v>9821</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ta Là Đạo Sĩ Mao Sơn, Sao Toàn Là Tà Thuật [Dịch]</t>
+          <t>Nguyên Lai Ta Là Tu Tiên Đại Lão [Convert]</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Đô Thị, Huyền Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Linh Dị, Huyền Nghi Thần Quái, Lãng Mạn Thanh Xuân</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -7498,11 +7498,11 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.4094</v>
+        <v>0.3806</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20799-ta-la-dao-si-mao-son-sao-toan-la-ta-thuat-dich</t>
+          <t>https://sitruyencv.com/story/9821-nguyen-lai-ta-la-tu-tien-dai-lao-convert</t>
         </is>
       </c>
     </row>
@@ -7514,7 +7514,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7526,29 +7526,29 @@
         <v>4</v>
       </c>
       <c r="E155" t="n">
-        <v>9820</v>
+        <v>171</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
+          <t>Thời Trung Cổ Truyền Kỳ Thợ Săn Quỷ [Convert]</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tây Phương Kỳ Huyễn</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.4039</v>
+        <v>0.3793</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/171-thoi-trung-co-truyen-ky-tho-san-quy-convert</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7572,29 +7572,29 @@
         <v>5</v>
       </c>
       <c r="E156" t="n">
-        <v>19317</v>
+        <v>20773</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kinh Hồng [Dịch]</t>
+          <t>Công tử đẹp trai quá [Dịch]</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Lịch Sử Quân Sự, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.3962</v>
+        <v>0.3785</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19317-kinh-hong-dich</t>
+          <t>https://sitruyencv.com/story/20773-cong-tu-dep-trai-qua-dich</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7618,16 +7618,16 @@
         <v>6</v>
       </c>
       <c r="E157" t="n">
-        <v>9821</v>
+        <v>15013</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nguyên Lai Ta Là Tu Tiên Đại Lão [Convert]</t>
+          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -7636,11 +7636,11 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.3955</v>
+        <v>0.3758</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9821-nguyen-lai-ta-la-tu-tien-dai-lao-convert</t>
+          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
         </is>
       </c>
     </row>
@@ -7652,7 +7652,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7664,29 +7664,29 @@
         <v>7</v>
       </c>
       <c r="E158" t="n">
-        <v>20259</v>
+        <v>18885</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Một Xà Đắc Đạo [Dịch]</t>
+          <t>Chiến Thần Cuồng Tiêu Chi Chư Thiên Vạn Giới [Convert]</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Điền Văn, Tiên Hiệp Kỳ Duyên, Huyền Nghi Thần Quái</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.3932</v>
+        <v>0.3717</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20259-mot-xa-dac-dao-dich</t>
+          <t>https://sitruyencv.com/story/18885-chien-than-cuong-tieu-chi-chu-thien-van-gioi-convert</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7710,16 +7710,16 @@
         <v>8</v>
       </c>
       <c r="E159" t="n">
-        <v>13514</v>
+        <v>20803</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mạnh Nhất Gia Tộc, Từ Khai Chi Tán Diệp Bắt Đầu [Convert]</t>
+          <t>Quỷ Đạo Tiên Lộ [Dịch]</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp, Linh Dị, Huyền Nghi Thần Quái</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7728,11 +7728,11 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.3923</v>
+        <v>0.3695</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13514-manh-nhat-gia-toc-tu-khai-chi-tan-diep-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/20803-quy-dao-tien-lo-dich</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7756,16 +7756,16 @@
         <v>9</v>
       </c>
       <c r="E160" t="n">
-        <v>13481</v>
+        <v>13514</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ta, Đạo Sĩ, Người Khoác Nho Sam, Vụng Trộm Phát Dục [Convert]</t>
+          <t>Mạnh Nhất Gia Tộc, Từ Khai Chi Tán Diệp Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Kiếm Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -7774,11 +7774,11 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0.3918</v>
+        <v>0.368</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13481-ta-dao-si-nguoi-khoac-nho-sam-vung-trom-phat-duc-convert</t>
+          <t>https://sitruyencv.com/story/13514-manh-nhat-gia-toc-tu-khai-chi-tan-diep-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Tìm truyện kỳ ảo</t>
+          <t>Tìm truyện tiên hiệp hơn 500 chương</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7802,16 +7802,16 @@
         <v>10</v>
       </c>
       <c r="E161" t="n">
-        <v>15013</v>
+        <v>17519</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
+          <t>Phi Thăng, Theo Thiên Địa Hỗn Độn Quyết Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -7820,11 +7820,11 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.391</v>
+        <v>0.3615</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
+          <t>https://sitruyencv.com/story/17519-phi-thang-theo-thien-dia-hon-don-quyet-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7848,29 +7848,29 @@
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>171</v>
+        <v>3280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Thời Trung Cổ Truyền Kỳ Thợ Săn Quỷ [Convert]</t>
+          <t>Tên Minh Tinh Này Rất Muốn Về Hưu [Convert]</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Tây Phương Kỳ Huyễn</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.3999</v>
+        <v>0.4269</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/171-thoi-trung-co-truyen-ky-tho-san-quy-convert</t>
+          <t>https://sitruyencv.com/story/3280-ten-minh-tinh-nay-rat-muon-ve-huu-convert</t>
         </is>
       </c>
     </row>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7894,16 +7894,16 @@
         <v>2</v>
       </c>
       <c r="E163" t="n">
-        <v>19312</v>
+        <v>19521</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nhật ký của Ninh Thư pháo hôi [Dịch]</t>
+          <t>Đại Minh Đã Mất, Ngươi Bảo Ta Nhậm Chức Cẩm Y Vệ? [Convert]</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Huyền Nghi, Hệ Thống, Xuyên Sách, Dị Năng, Nữ Cường, Nữ Phụ, Trinh Thám, Huyền Huyễn Ngôn Tình, Tiên Hiệp Kỳ Duyên</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -7912,11 +7912,11 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0.3954</v>
+        <v>0.4153</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19312-nhat-ky-cua-ninh-thu-phao-hoi-dich</t>
+          <t>https://sitruyencv.com/story/19521-dai-minh-da-mat-nguoi-bao-ta-nham-chuc-cam-y-ve-convert</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>3</v>
       </c>
       <c r="E164" t="n">
-        <v>13970</v>
+        <v>19710</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nạn Đói Năm, Ta Dùng Mỗi Ngày Tình Báo, Nạp Thiếp Ăn Thịt [Convert]</t>
+          <t>Sau Ly Hôn, Họ Lại Theo Đuổi Tôi [Dịch]</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dã Sử</t>
+          <t>Đô Thị, Sủng</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7958,11 +7958,11 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.3914</v>
+        <v>0.4014</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13970-nan-doi-nam-ta-dung-moi-ngay-tinh-bao-nap-thiep-an-thit-convert</t>
+          <t>https://sitruyencv.com/story/19710-sau-ly-hon-ho-lai-theo-duoi-toi-dich</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7986,11 +7986,11 @@
         <v>4</v>
       </c>
       <c r="E165" t="n">
-        <v>17487</v>
+        <v>20777</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Xuyên Qua Sáu Số Không: Ta Có Một Cái Vạn Năng Nông Trường [Convert]</t>
+          <t>Bậc Thầy Đóng Vai: Bắt Đầu Từ Chuyên Gia Chia Tay [Dịch]</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -8000,15 +8000,15 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0.3854</v>
+        <v>0.3919</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17487-xuyen-qua-sau-so-khong-ta-co-mot-cai-van-nang-nong-truong-convert</t>
+          <t>https://sitruyencv.com/story/20777-bac-thay-dong-vai-bat-dau-tu-chuyen-gia-chia-tay-dich</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -8032,16 +8032,16 @@
         <v>5</v>
       </c>
       <c r="E166" t="n">
-        <v>16290</v>
+        <v>17650</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tổng Mạn: Từ Mushoku Tensei Bắt Đầu [Convert]</t>
+          <t>Toàn Dân Hôn Phối: Tốt Nghiệp Phát Lão Bà, Chơi Hỏng Long Nương [Convert]</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -8050,11 +8050,11 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.3811</v>
+        <v>0.3864</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16290-tong-man-tu-mushoku-tensei-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/17650-toan-dan-hon-phoi-tot-nghiep-phat-lao-ba-choi-hong-long-nuong-convert</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8078,16 +8078,16 @@
         <v>6</v>
       </c>
       <c r="E167" t="n">
-        <v>13514</v>
+        <v>18703</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Mạnh Nhất Gia Tộc, Từ Khai Chi Tán Diệp Bắt Đầu [Convert]</t>
+          <t>Thần Bí Khôi Phục: Nếu [Convert]</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đồng Nhân, Huyền Nghi, Linh Dị</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -8096,11 +8096,11 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.3806</v>
+        <v>0.3844</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13514-manh-nhat-gia-toc-tu-khai-chi-tan-diep-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/18703-than-bi-khoi-phuc-neu-convert</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8124,29 +8124,29 @@
         <v>7</v>
       </c>
       <c r="E168" t="n">
-        <v>19472</v>
+        <v>17487</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Đại Minh: Bắt Đầu Cứu Người Đáng Giết [Convert]</t>
+          <t>Xuyên Qua Sáu Số Không: Ta Có Một Cái Vạn Năng Nông Trường [Convert]</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dã Sử</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.38</v>
+        <v>0.3823</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19472-dai-minh-bat-dau-cuu-nguoi-dang-giet-convert</t>
+          <t>https://sitruyencv.com/story/17487-xuyen-qua-sau-so-khong-ta-co-mot-cai-van-nang-nong-truong-convert</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8170,29 +8170,29 @@
         <v>8</v>
       </c>
       <c r="E169" t="n">
-        <v>20775</v>
+        <v>19836</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tất Cả Theo Cẩm Y Vệ Bắt Đầu [Dịch]</t>
+          <t>Bắt Đầu Chớp Nhoáng Kết Hôn Với Chủ Nhiệm, Trời Giáng Tài Sản Nghìn Tỷ [Convert]</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Kiếm Hiệp, Hệ Thống, Huyền Nghi Thần Quái</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.3754</v>
+        <v>0.3799</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20775-tat-ca-theo-cam-y-ve-bat-dau-dich</t>
+          <t>https://sitruyencv.com/story/19836-bat-dau-chop-nhoang-ket-hon-voi-chu-nhiem-troi-giang-tai-san-nghin-ty-convert</t>
         </is>
       </c>
     </row>
@@ -8204,7 +8204,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8216,16 +8216,16 @@
         <v>9</v>
       </c>
       <c r="E170" t="n">
-        <v>20259</v>
+        <v>16395</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Một Xà Đắc Đạo [Dịch]</t>
+          <t>Quan Trường: Ta Viết Lại Nhân Sinh Kịch Bản [Convert]</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Điền Văn, Tiên Hiệp Kỳ Duyên, Huyền Nghi Thần Quái</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -8234,11 +8234,11 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.3749</v>
+        <v>0.3777</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20259-mot-xa-dac-dao-dich</t>
+          <t>https://sitruyencv.com/story/16395-quan-truong-ta-viet-lai-nhan-sinh-kich-ban-convert</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Tìm truyện xuyên sách</t>
+          <t>Tìm truyện đô thị trạng thái đã hoàn thành</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8262,16 +8262,16 @@
         <v>10</v>
       </c>
       <c r="E171" t="n">
-        <v>16211</v>
+        <v>12662</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Đấu La: Từ Võ Hồn Thời Chi Trùng Bắt Đầu [Convert]</t>
+          <t>Theo Nuốt Riêng Ngàn Vạn Ức Liếm Cẩu Kim Bắt Đầu Làm Thần Hào [Convert]</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -8280,11 +8280,11 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.3727</v>
+        <v>0.374</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16211-dau-la-tu-vo-hon-thoi-chi-trung-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/12662-theo-nuot-rieng-ngan-van-uc-liem-cau-kim-bat-dau-lam-than-hao-convert</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8308,11 +8308,11 @@
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>12188</v>
+        <v>8979</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Thiên Tai Tận Thế, Nàng Trữ Đầy Vật Tư Phía Sau Giết Điên Rồi [Convert]</t>
+          <t>70 Quân Hôn Binh Vương Đầu Quả Tim Sủng [Convert]</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -8322,15 +8322,15 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.4063</v>
+        <v>0.4052</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12188-thien-tai-tan-the-nang-tru-day-vat-tu-phia-sau-giet-dien-roi-convert</t>
+          <t>https://sitruyencv.com/story/8979-70-quan-hon-binh-vuong-dau-qua-tim-sung-convert</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>0.3993</v>
+        <v>0.4017</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8400,16 +8400,16 @@
         <v>3</v>
       </c>
       <c r="E174" t="n">
-        <v>16145</v>
+        <v>12188</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Liếm Cẩu Phản Diện Chỉ Nghĩ Cẩu , Nữ Chính Không Theo Sáo Lộ Đi [Convert]</t>
+          <t>Thiên Tai Tận Thế, Nàng Trữ Đầy Vật Tư Phía Sau Giết Điên Rồi [Convert]</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -8418,11 +8418,11 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.3671</v>
+        <v>0.3937</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16145-liem-cau-phan-dien-chi-nghi-cau-nu-chinh-khong-theo-sao-lo-di-convert</t>
+          <t>https://sitruyencv.com/story/12188-thien-tai-tan-the-nang-tru-day-vat-tu-phia-sau-giet-dien-roi-convert</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8446,16 +8446,16 @@
         <v>4</v>
       </c>
       <c r="E175" t="n">
-        <v>20595</v>
+        <v>17487</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Trùng Sinh Trở Lại Năm 1991 Làm Nhà Giàu Nhất [Dịch]</t>
+          <t>Xuyên Qua Sáu Số Không: Ta Có Một Cái Vạn Năng Nông Trường [Convert]</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Đô Thị, Light Novel, Ẩm Thực, Cận Đại, Điền Văn, Ngôn Tình, Lãng Mạn Thanh Xuân</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -8464,11 +8464,11 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>0.3644</v>
+        <v>0.3833</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20595-trung-sinh-tro-lai-nam-1991-lam-nha-giau-nhat-dich</t>
+          <t>https://sitruyencv.com/story/17487-xuyen-qua-sau-so-khong-ta-co-mot-cai-van-nang-nong-truong-convert</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8492,16 +8492,16 @@
         <v>5</v>
       </c>
       <c r="E176" t="n">
-        <v>20632</v>
+        <v>20353</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Bạn Gái Hờ Của Tôi Đang Dốc Sức Phòng Thủ Trước Sự Tấn Công Của Các Cô Ấy [Dịch]</t>
+          <t>Từ Gia Phả Bắt Đầu Xây Dựng Trường Sinh Thế Gia [Dịch]</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Thanh Xuân Vườn Trường, Điền Văn, Ngôn Tình, Lãng Mạn Thanh Xuân</t>
+          <t>Huyền Huyễn, Điền Văn</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -8510,11 +8510,11 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.3591</v>
+        <v>0.3574</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20632-ban-gai-ho-cua-toi-dang-doc-suc-phong-thu-truoc-su-tan-cong-cua-cac-co-ay-dich</t>
+          <t>https://sitruyencv.com/story/20353-tu-gia-pha-bat-dau-xay-dung-truong-sinh-the-gia-dich</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8538,16 +8538,16 @@
         <v>6</v>
       </c>
       <c r="E177" t="n">
-        <v>15093</v>
+        <v>20632</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Ngộ Tính Nghịch Thiên, Ta Ở Hogwarts Xây Phù Không Thành [Convert]</t>
+          <t>Bạn Gái Hờ Của Tôi Đang Dốc Sức Phòng Thủ Trước Sự Tấn Công Của Các Cô Ấy [Dịch]</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Thanh Xuân Vườn Trường, Điền Văn, Ngôn Tình, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -8556,11 +8556,11 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.3576</v>
+        <v>0.3553</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15093-ngo-tinh-nghich-thien-ta-o-hogwarts-xay-phu-khong-thanh-convert</t>
+          <t>https://sitruyencv.com/story/20632-ban-gai-ho-cua-toi-dang-doc-suc-phong-thu-truoc-su-tan-cong-cua-cac-co-ay-dich</t>
         </is>
       </c>
     </row>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8584,16 +8584,16 @@
         <v>7</v>
       </c>
       <c r="E178" t="n">
-        <v>17487</v>
+        <v>8416</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Xuyên Qua Sáu Số Không: Ta Có Một Cái Vạn Năng Nông Trường [Convert]</t>
+          <t>70 Ta Thành Nữ Chủ Cực Phẩm Tam Tẩu [Convert]</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -8602,11 +8602,11 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.3533</v>
+        <v>0.3541</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17487-xuyen-qua-sau-so-khong-ta-co-mot-cai-van-nang-nong-truong-convert</t>
+          <t>https://sitruyencv.com/story/8416-70-ta-thanh-nu-chu-cuc-pham-tam-tau-convert</t>
         </is>
       </c>
     </row>
@@ -8618,7 +8618,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8630,29 +8630,29 @@
         <v>8</v>
       </c>
       <c r="E179" t="n">
-        <v>8416</v>
+        <v>12297</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>70 Ta Thành Nữ Chủ Cực Phẩm Tam Tẩu [Convert]</t>
+          <t>Ta Tại Tu Tiên Thế Giới Mở Nông Trường [Convert]</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.3479</v>
+        <v>0.3503</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8416-70-ta-thanh-nu-chu-cuc-pham-tam-tau-convert</t>
+          <t>https://sitruyencv.com/story/12297-ta-tai-tu-tien-the-gioi-mo-nong-truong-convert</t>
         </is>
       </c>
     </row>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8676,16 +8676,16 @@
         <v>9</v>
       </c>
       <c r="E180" t="n">
-        <v>9821</v>
+        <v>2021</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nguyên Lai Ta Là Tu Tiên Đại Lão [Convert]</t>
+          <t>Dựa Vào Làm Ruộng Đi Lên Đỉnh Cao Nhân Sinh [Convert]</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Cổ Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9821-nguyen-lai-ta-la-tu-tien-dai-lao-convert</t>
+          <t>https://sitruyencv.com/story/2021-dua-vao-lam-ruong-di-len-dinh-cao-nhan-sinh-convert</t>
         </is>
       </c>
     </row>
@@ -8710,7 +8710,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Tìm truyện hiện đại ngôn tình</t>
+          <t>Tìm truyện hiện đại ngôn tình trạng thái đang ra</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8722,16 +8722,16 @@
         <v>10</v>
       </c>
       <c r="E181" t="n">
-        <v>8979</v>
+        <v>17785</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>70 Quân Hôn Binh Vương Đầu Quả Tim Sủng [Convert]</t>
+          <t>Võng Du: Ta Ở Trong Game Làm Quan Sai [Convert]</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Võng Du</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -8740,11 +8740,11 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>0.3441</v>
+        <v>0.346</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8979-70-quan-hon-binh-vuong-dau-qua-tim-sung-convert</t>
+          <t>https://sitruyencv.com/story/17785-vong-du-ta-o-trong-game-lam-quan-sai-convert</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0.4689</v>
+        <v>0.4479</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8832,7 +8832,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0.437</v>
+        <v>0.4131</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>0.4162</v>
+        <v>0.3678</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8906,11 +8906,11 @@
         <v>4</v>
       </c>
       <c r="E185" t="n">
-        <v>13514</v>
+        <v>11756</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mạnh Nhất Gia Tộc, Từ Khai Chi Tán Diệp Bắt Đầu [Convert]</t>
+          <t>Ta Có Vô Hạn Tử Sĩ, Bạo Binh Quét Ngang Chư Thiên [Convert]</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -8924,11 +8924,11 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.4002</v>
+        <v>0.3601</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13514-manh-nhat-gia-toc-tu-khai-chi-tan-diep-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/11756-ta-co-vo-han-tu-si-bao-binh-quet-ngang-chu-thien-convert</t>
         </is>
       </c>
     </row>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8952,29 +8952,29 @@
         <v>5</v>
       </c>
       <c r="E186" t="n">
-        <v>12068</v>
+        <v>20775</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Cửu Tinh Bá Thể Quyết [Convert]</t>
+          <t>Tất Cả Theo Cẩm Y Vệ Bắt Đầu [Dịch]</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Kiếm Hiệp, Hệ Thống, Huyền Nghi Thần Quái</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0.3975</v>
+        <v>0.36</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12068-cuu-tinh-ba-the-quyet-convert</t>
+          <t>https://sitruyencv.com/story/20775-tat-ca-theo-cam-y-ve-bat-dau-dich</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8998,29 +8998,29 @@
         <v>6</v>
       </c>
       <c r="E187" t="n">
-        <v>18262</v>
+        <v>14103</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Thần Bí Khôi Phục : Từ Quỷ Tranh Vẽ Bắt Đầu [Convert]</t>
+          <t>Đấu Phá: Mỗi Ngày Cơ Duyên! Các Nàng Đều Cầu Ta Chỉ Giáo [Convert]</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Huyền Nghi, Huyền Nghi Thần Quái</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0.3854</v>
+        <v>0.3578</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18262-than-bi-khoi-phuc-tu-quy-tranh-ve-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/14103-dau-pha-moi-ngay-co-duyen-cac-nang-deu-cau-ta-chi-giao-convert</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -9044,11 +9044,11 @@
         <v>7</v>
       </c>
       <c r="E188" t="n">
-        <v>2385</v>
+        <v>11918</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tối Cường Hệ Thống [Convert]</t>
+          <t>Ngự Thú Tiến Hóa Thương [Convert]</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -9062,11 +9062,11 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>0.3818</v>
+        <v>0.3576</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/2385-toi-cuong-he-thong-convert</t>
+          <t>https://sitruyencv.com/story/11918-ngu-thu-tien-hoa-thuong-convert</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -9090,29 +9090,29 @@
         <v>8</v>
       </c>
       <c r="E189" t="n">
-        <v>14222</v>
+        <v>13674</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gia Tộc Tu Tiên: Ta Làm Trấn Tộc Linh Thú [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.3784</v>
+        <v>0.355</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14222-gia-toc-tu-tien-ta-lam-tran-toc-linh-thu-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -9136,11 +9136,11 @@
         <v>9</v>
       </c>
       <c r="E190" t="n">
-        <v>3074</v>
+        <v>18885</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Trộm Mộ: Bắt Đầu Triệu Hoán Bất Lương Soái, Nộ Tình Tương Tây [Convert]</t>
+          <t>Chiến Thần Cuồng Tiêu Chi Chư Thiên Vạn Giới [Convert]</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -9154,11 +9154,11 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.3779</v>
+        <v>0.3539</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/3074-trom-mo-bat-dau-trieu-hoan-bat-luong-soai-no-tinh-tuong-tay-convert</t>
+          <t>https://sitruyencv.com/story/18885-chien-than-cuong-tieu-chi-chu-thien-van-gioi-convert</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tìm truyện tây phương kỳ huyễn</t>
+          <t>Tìm truyện tây phương kỳ huyễn ít hơn 200 chương</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -9182,11 +9182,11 @@
         <v>10</v>
       </c>
       <c r="E191" t="n">
-        <v>9820</v>
+        <v>3074</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
+          <t>Trộm Mộ: Bắt Đầu Triệu Hoán Bất Lương Soái, Nộ Tình Tương Tây [Convert]</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -9196,15 +9196,15 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.3771</v>
+        <v>0.3488</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/3074-trom-mo-bat-dau-trieu-hoan-bat-luong-soai-no-tinh-tuong-tay-convert</t>
         </is>
       </c>
     </row>
@@ -17036,7 +17036,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -17048,29 +17048,29 @@
         <v>1</v>
       </c>
       <c r="E362" t="n">
-        <v>171</v>
+        <v>8524</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Thời Trung Cổ Truyền Kỳ Thợ Săn Quỷ [Convert]</t>
+          <t>Mạt Thế Trọng Sinh: Tuyệt Sắc Pháo Hôi Đại Tiểu Thư Nghịch Tập [Convert]</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Tây Phương Kỳ Huyễn</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I362" t="n">
-        <v>0.4509</v>
+        <v>0.4525</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/171-thoi-trung-co-truyen-ky-tho-san-quy-convert</t>
+          <t>https://sitruyencv.com/story/8524-mat-the-trong-sinh-tuyet-sac-phao-hoi-dai-tieu-thu-nghich-tap-convert</t>
         </is>
       </c>
     </row>
@@ -17082,7 +17082,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -17094,29 +17094,29 @@
         <v>2</v>
       </c>
       <c r="E363" t="n">
-        <v>20799</v>
+        <v>171</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Ta Là Đạo Sĩ Mao Sơn, Sao Toàn Là Tà Thuật [Dịch]</t>
+          <t>Thời Trung Cổ Truyền Kỳ Thợ Săn Quỷ [Convert]</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Đô Thị, Huyền Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Linh Dị, Huyền Nghi Thần Quái, Lãng Mạn Thanh Xuân</t>
+          <t>Tây Phương Kỳ Huyễn</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I363" t="n">
-        <v>0.4334</v>
+        <v>0.4278</v>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20799-ta-la-dao-si-mao-son-sao-toan-la-ta-thuat-dich</t>
+          <t>https://sitruyencv.com/story/171-thoi-trung-co-truyen-ky-tho-san-quy-convert</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -17140,29 +17140,29 @@
         <v>3</v>
       </c>
       <c r="E364" t="n">
-        <v>12188</v>
+        <v>20799</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Thiên Tai Tận Thế, Nàng Trữ Đầy Vật Tư Phía Sau Giết Điên Rồi [Convert]</t>
+          <t>Ta Là Đạo Sĩ Mao Sơn, Sao Toàn Là Tà Thuật [Dịch]</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Đô Thị, Huyền Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Linh Dị, Huyền Nghi Thần Quái, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I364" t="n">
-        <v>0.4321</v>
+        <v>0.4276</v>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12188-thien-tai-tan-the-nang-tru-day-vat-tu-phia-sau-giet-dien-roi-convert</t>
+          <t>https://sitruyencv.com/story/20799-ta-la-dao-si-mao-son-sao-toan-la-ta-thuat-dich</t>
         </is>
       </c>
     </row>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -17186,11 +17186,11 @@
         <v>4</v>
       </c>
       <c r="E365" t="n">
-        <v>9820</v>
+        <v>18885</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
+          <t>Chiến Thần Cuồng Tiêu Chi Chư Thiên Vạn Giới [Convert]</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -17200,15 +17200,15 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I365" t="n">
-        <v>0.4281</v>
+        <v>0.4205</v>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/18885-chien-than-cuong-tieu-chi-chu-thien-van-gioi-convert</t>
         </is>
       </c>
     </row>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -17232,29 +17232,29 @@
         <v>5</v>
       </c>
       <c r="E366" t="n">
-        <v>8524</v>
+        <v>12428</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Mạt Thế Trọng Sinh: Tuyệt Sắc Pháo Hôi Đại Tiểu Thư Nghịch Tập [Convert]</t>
+          <t>Đấu La: Thần Cấp Máy Gian Lận, Rời Núi Tức Vô Địch [Convert]</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I366" t="n">
-        <v>0.4249</v>
+        <v>0.4203</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8524-mat-the-trong-sinh-tuyet-sac-phao-hoi-dai-tieu-thu-nghich-tap-convert</t>
+          <t>https://sitruyencv.com/story/12428-dau-la-than-cap-may-gian-lan-roi-nui-tuc-vo-dich-convert</t>
         </is>
       </c>
     </row>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -17278,16 +17278,16 @@
         <v>6</v>
       </c>
       <c r="E367" t="n">
-        <v>13183</v>
+        <v>16537</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Đệ Cửu Đế Quốc [Convert]</t>
+          <t>Tống Võ: Đại Tần Hoàng Tử, Các Ngươi Tu Võ Ta Tu Tiên [Convert]</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -17296,11 +17296,11 @@
         </is>
       </c>
       <c r="I367" t="n">
-        <v>0.417</v>
+        <v>0.4202</v>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13183-de-cuu-de-quoc-convert</t>
+          <t>https://sitruyencv.com/story/16537-tong-vo-dai-tan-hoang-tu-cac-nguoi-tu-vo-ta-tu-tien-convert</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -17324,29 +17324,29 @@
         <v>7</v>
       </c>
       <c r="E368" t="n">
-        <v>20259</v>
+        <v>12188</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Một Xà Đắc Đạo [Dịch]</t>
+          <t>Thiên Tai Tận Thế, Nàng Trữ Đầy Vật Tư Phía Sau Giết Điên Rồi [Convert]</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Điền Văn, Tiên Hiệp Kỳ Duyên, Huyền Nghi Thần Quái</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I368" t="n">
-        <v>0.4152</v>
+        <v>0.4199</v>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20259-mot-xa-dac-dao-dich</t>
+          <t>https://sitruyencv.com/story/12188-thien-tai-tan-the-nang-tru-day-vat-tu-phia-sau-giet-dien-roi-convert</t>
         </is>
       </c>
     </row>
@@ -17358,7 +17358,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -17370,29 +17370,29 @@
         <v>8</v>
       </c>
       <c r="E369" t="n">
-        <v>12428</v>
+        <v>20259</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Đấu La: Thần Cấp Máy Gian Lận, Rời Núi Tức Vô Địch [Convert]</t>
+          <t>Một Xà Đắc Đạo [Dịch]</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Tiên Hiệp, Điền Văn, Tiên Hiệp Kỳ Duyên, Huyền Nghi Thần Quái</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I369" t="n">
-        <v>0.4134</v>
+        <v>0.4177</v>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12428-dau-la-than-cap-may-gian-lan-roi-nui-tuc-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/20259-mot-xa-dac-dao-dich</t>
         </is>
       </c>
     </row>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -17416,16 +17416,16 @@
         <v>9</v>
       </c>
       <c r="E370" t="n">
-        <v>14103</v>
+        <v>13183</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Đấu Phá: Mỗi Ngày Cơ Duyên! Các Nàng Đều Cầu Ta Chỉ Giáo [Convert]</t>
+          <t>Đệ Cửu Đế Quốc [Convert]</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -17434,11 +17434,11 @@
         </is>
       </c>
       <c r="I370" t="n">
-        <v>0.4133</v>
+        <v>0.4166</v>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14103-dau-pha-moi-ngay-co-duyen-cac-nang-deu-cau-ta-chi-giao-convert</t>
+          <t>https://sitruyencv.com/story/13183-de-cuu-de-quoc-convert</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Tìm truyện có bối cảnh dị thế đại lục</t>
+          <t>Tìm truyện có bối cảnh dị thế đại lục, trang thái truyện đã hoàn thành</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -17462,11 +17462,11 @@
         <v>10</v>
       </c>
       <c r="E371" t="n">
-        <v>11918</v>
+        <v>15013</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Ngự Thú Tiến Hóa Thương [Convert]</t>
+          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -17480,11 +17480,11 @@
         </is>
       </c>
       <c r="I371" t="n">
-        <v>0.4102</v>
+        <v>0.41</v>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/11918-ngu-thu-tien-hoa-thuong-convert</t>
+          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
         </is>
       </c>
     </row>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -17508,29 +17508,29 @@
         <v>1</v>
       </c>
       <c r="E372" t="n">
-        <v>17487</v>
+        <v>18703</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Xuyên Qua Sáu Số Không: Ta Có Một Cái Vạn Năng Nông Trường [Convert]</t>
+          <t>Thần Bí Khôi Phục: Nếu [Convert]</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Đồng Nhân, Huyền Nghi, Linh Dị</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I372" t="n">
-        <v>0.4167</v>
+        <v>0.363</v>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17487-xuyen-qua-sau-so-khong-ta-co-mot-cai-van-nang-nong-truong-convert</t>
+          <t>https://sitruyencv.com/story/18703-than-bi-khoi-phuc-neu-convert</t>
         </is>
       </c>
     </row>
@@ -17542,7 +17542,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -17554,11 +17554,11 @@
         <v>2</v>
       </c>
       <c r="E373" t="n">
-        <v>20777</v>
+        <v>17487</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Bậc Thầy Đóng Vai: Bắt Đầu Từ Chuyên Gia Chia Tay [Dịch]</t>
+          <t>Xuyên Qua Sáu Số Không: Ta Có Một Cái Vạn Năng Nông Trường [Convert]</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -17568,15 +17568,15 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I373" t="n">
-        <v>0.413</v>
+        <v>0.3587</v>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20777-bac-thay-dong-vai-bat-dau-tu-chuyen-gia-chia-tay-dich</t>
+          <t>https://sitruyencv.com/story/17487-xuyen-qua-sau-so-khong-ta-co-mot-cai-van-nang-nong-truong-convert</t>
         </is>
       </c>
     </row>
@@ -17588,7 +17588,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -17600,16 +17600,16 @@
         <v>3</v>
       </c>
       <c r="E374" t="n">
-        <v>20799</v>
+        <v>19019</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Ta Là Đạo Sĩ Mao Sơn, Sao Toàn Là Tà Thuật [Dịch]</t>
+          <t>Thần Tuyển Lạc Viên [Dịch]</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Đô Thị, Huyền Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Linh Dị, Huyền Nghi Thần Quái, Lãng Mạn Thanh Xuân</t>
+          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -17618,11 +17618,11 @@
         </is>
       </c>
       <c r="I374" t="n">
-        <v>0.4121</v>
+        <v>0.3525</v>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20799-ta-la-dao-si-mao-son-sao-toan-la-ta-thuat-dich</t>
+          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
         </is>
       </c>
     </row>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -17646,29 +17646,29 @@
         <v>4</v>
       </c>
       <c r="E375" t="n">
-        <v>20259</v>
+        <v>13674</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Một Xà Đắc Đạo [Dịch]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Điền Văn, Tiên Hiệp Kỳ Duyên, Huyền Nghi Thần Quái</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I375" t="n">
-        <v>0.4035</v>
+        <v>0.3493</v>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20259-mot-xa-dac-dao-dich</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -17680,7 +17680,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -17692,29 +17692,29 @@
         <v>5</v>
       </c>
       <c r="E376" t="n">
-        <v>18703</v>
+        <v>20799</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Thần Bí Khôi Phục: Nếu [Convert]</t>
+          <t>Ta Là Đạo Sĩ Mao Sơn, Sao Toàn Là Tà Thuật [Dịch]</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Đồng Nhân, Huyền Nghi, Linh Dị</t>
+          <t>Đô Thị, Huyền Huyễn, Kỳ Ảo, Tây Phương Kỳ Huyễn, Linh Dị, Huyền Nghi Thần Quái, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I376" t="n">
-        <v>0.4013</v>
+        <v>0.3482</v>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18703-than-bi-khoi-phuc-neu-convert</t>
+          <t>https://sitruyencv.com/story/20799-ta-la-dao-si-mao-son-sao-toan-la-ta-thuat-dich</t>
         </is>
       </c>
     </row>
@@ -17726,7 +17726,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -17738,29 +17738,29 @@
         <v>6</v>
       </c>
       <c r="E377" t="n">
-        <v>16145</v>
+        <v>20595</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Liếm Cẩu Phản Diện Chỉ Nghĩ Cẩu , Nữ Chính Không Theo Sáo Lộ Đi [Convert]</t>
+          <t>Trùng Sinh Trở Lại Năm 1991 Làm Nhà Giàu Nhất [Dịch]</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Đô Thị, Light Novel, Ẩm Thực, Cận Đại, Điền Văn, Ngôn Tình, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I377" t="n">
-        <v>0.39</v>
+        <v>0.3481</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16145-liem-cau-phan-dien-chi-nghi-cau-nu-chinh-khong-theo-sao-lo-di-convert</t>
+          <t>https://sitruyencv.com/story/20595-trung-sinh-tro-lai-nam-1991-lam-nha-giau-nhat-dich</t>
         </is>
       </c>
     </row>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -17784,29 +17784,29 @@
         <v>7</v>
       </c>
       <c r="E378" t="n">
-        <v>20595</v>
+        <v>16145</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Trùng Sinh Trở Lại Năm 1991 Làm Nhà Giàu Nhất [Dịch]</t>
+          <t>Liếm Cẩu Phản Diện Chỉ Nghĩ Cẩu , Nữ Chính Không Theo Sáo Lộ Đi [Convert]</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Đô Thị, Light Novel, Ẩm Thực, Cận Đại, Điền Văn, Ngôn Tình, Lãng Mạn Thanh Xuân</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I378" t="n">
-        <v>0.387</v>
+        <v>0.3453</v>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20595-trung-sinh-tro-lai-nam-1991-lam-nha-giau-nhat-dich</t>
+          <t>https://sitruyencv.com/story/16145-liem-cau-phan-dien-chi-nghi-cau-nu-chinh-khong-theo-sao-lo-di-convert</t>
         </is>
       </c>
     </row>
@@ -17818,7 +17818,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -17830,16 +17830,16 @@
         <v>8</v>
       </c>
       <c r="E379" t="n">
-        <v>19019</v>
+        <v>17349</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Thần Tuyển Lạc Viên [Dịch]</t>
+          <t>Cùng Nữ Chủ Thuê Nhà Ở Chung Về Sau, Ta Nhìn Thấy Ẩn Tàng Tin Tức [Convert]</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -17848,11 +17848,11 @@
         </is>
       </c>
       <c r="I379" t="n">
-        <v>0.3813</v>
+        <v>0.3427</v>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
+          <t>https://sitruyencv.com/story/17349-cung-nu-chu-thue-nha-o-chung-ve-sau-ta-nhin-thay-an-tang-tin-tuc-convert</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -17876,29 +17876,29 @@
         <v>9</v>
       </c>
       <c r="E380" t="n">
-        <v>20532</v>
+        <v>19521</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Vai Ác: Bắt Đầu Đánh Mặt Chiến Thần, Nữ Tổng Giám Đốc Giúp Ta Xuất Khí [Dịch]</t>
+          <t>Đại Minh Đã Mất, Ngươi Bảo Ta Nhậm Chức Cẩm Y Vệ? [Convert]</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Đô Thị, Hệ Thống, Xuyên Sách</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I380" t="n">
-        <v>0.3762</v>
+        <v>0.3411</v>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20532-vai-ac-bat-dau-danh-mat-chien-than-nu-tong-giam-doc-giup-ta-xuat-khi-dich</t>
+          <t>https://sitruyencv.com/story/19521-dai-minh-da-mat-nguoi-bao-ta-nham-chuc-cam-y-ve-convert</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Tìm truyện đô thị có yếu tố dị năng</t>
+          <t>Tìm truyện đô thị có yếu tố dị năng có hơn 300 chương</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -17922,16 +17922,16 @@
         <v>10</v>
       </c>
       <c r="E381" t="n">
-        <v>17349</v>
+        <v>20532</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Cùng Nữ Chủ Thuê Nhà Ở Chung Về Sau, Ta Nhìn Thấy Ẩn Tàng Tin Tức [Convert]</t>
+          <t>Vai Ác: Bắt Đầu Đánh Mặt Chiến Thần, Nữ Tổng Giám Đốc Giúp Ta Xuất Khí [Dịch]</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Đô Thị, Hệ Thống, Xuyên Sách</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -17940,11 +17940,11 @@
         </is>
       </c>
       <c r="I381" t="n">
-        <v>0.3734</v>
+        <v>0.3382</v>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17349-cung-nu-chu-thue-nha-o-chung-ve-sau-ta-nhin-thay-an-tang-tin-tuc-convert</t>
+          <t>https://sitruyencv.com/story/20532-vai-ac-bat-dau-danh-mat-chien-than-nu-tong-giam-doc-giup-ta-xuat-khi-dich</t>
         </is>
       </c>
     </row>
@@ -17956,7 +17956,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -17986,7 +17986,7 @@
         </is>
       </c>
       <c r="I382" t="n">
-        <v>0.4188</v>
+        <v>0.3688</v>
       </c>
       <c r="J382" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -18032,7 +18032,7 @@
         </is>
       </c>
       <c r="I383" t="n">
-        <v>0.4142</v>
+        <v>0.3679</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -18060,16 +18060,16 @@
         <v>3</v>
       </c>
       <c r="E384" t="n">
-        <v>17916</v>
+        <v>20353</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Từ Thiết Y Công Bắt Đầu Nhục Thân Thành Thánh [Convert]</t>
+          <t>Từ Gia Phả Bắt Đầu Xây Dựng Trường Sinh Thế Gia [Dịch]</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Huyền Huyễn, Điền Văn</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -18078,11 +18078,11 @@
         </is>
       </c>
       <c r="I384" t="n">
-        <v>0.4054</v>
+        <v>0.3443</v>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17916-tu-thiet-y-cong-bat-dau-nhuc-than-thanh-thanh-convert</t>
+          <t>https://sitruyencv.com/story/20353-tu-gia-pha-bat-dau-xay-dung-truong-sinh-the-gia-dich</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -18106,16 +18106,16 @@
         <v>4</v>
       </c>
       <c r="E385" t="n">
-        <v>12188</v>
+        <v>14103</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Thiên Tai Tận Thế, Nàng Trữ Đầy Vật Tư Phía Sau Giết Điên Rồi [Convert]</t>
+          <t>Đấu Phá: Mỗi Ngày Cơ Duyên! Các Nàng Đều Cầu Ta Chỉ Giáo [Convert]</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -18124,11 +18124,11 @@
         </is>
       </c>
       <c r="I385" t="n">
-        <v>0.3978</v>
+        <v>0.343</v>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12188-thien-tai-tan-the-nang-tru-day-vat-tu-phia-sau-giet-dien-roi-convert</t>
+          <t>https://sitruyencv.com/story/14103-dau-pha-moi-ngay-co-duyen-cac-nang-deu-cau-ta-chi-giao-convert</t>
         </is>
       </c>
     </row>
@@ -18140,7 +18140,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -18152,29 +18152,29 @@
         <v>5</v>
       </c>
       <c r="E386" t="n">
-        <v>17533</v>
+        <v>12188</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Vô Địch Theo Cướp Đoạt Khí Huyết Bắt Đầu [Convert]</t>
+          <t>Thiên Tai Tận Thế, Nàng Trữ Đầy Vật Tư Phía Sau Giết Điên Rồi [Convert]</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I386" t="n">
-        <v>0.3959</v>
+        <v>0.3419</v>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17533-vo-dich-theo-cuop-doat-khi-huyet-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/12188-thien-tai-tan-the-nang-tru-day-vat-tu-phia-sau-giet-dien-roi-convert</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -18198,16 +18198,16 @@
         <v>6</v>
       </c>
       <c r="E387" t="n">
-        <v>20353</v>
+        <v>17916</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Từ Gia Phả Bắt Đầu Xây Dựng Trường Sinh Thế Gia [Dịch]</t>
+          <t>Từ Thiết Y Công Bắt Đầu Nhục Thân Thành Thánh [Convert]</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Huyền Huyễn, Điền Văn</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -18216,11 +18216,11 @@
         </is>
       </c>
       <c r="I387" t="n">
-        <v>0.3921</v>
+        <v>0.336</v>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20353-tu-gia-pha-bat-dau-xay-dung-truong-sinh-the-gia-dich</t>
+          <t>https://sitruyencv.com/story/17916-tu-thiet-y-cong-bat-dau-nhuc-than-thanh-thanh-convert</t>
         </is>
       </c>
     </row>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -18244,16 +18244,16 @@
         <v>7</v>
       </c>
       <c r="E388" t="n">
-        <v>19317</v>
+        <v>13739</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Kinh Hồng [Dịch]</t>
+          <t>Đa Tử Đa Phúc, Bắt Đầu Liền Đưa Tuyệt Mỹ Lão Bà [Convert]</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Lịch Sử Quân Sự, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -18262,11 +18262,11 @@
         </is>
       </c>
       <c r="I388" t="n">
-        <v>0.3914</v>
+        <v>0.3349</v>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19317-kinh-hong-dich</t>
+          <t>https://sitruyencv.com/story/13739-da-tu-da-phuc-bat-dau-lien-dua-tuyet-my-lao-ba-convert</t>
         </is>
       </c>
     </row>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -18290,11 +18290,11 @@
         <v>8</v>
       </c>
       <c r="E389" t="n">
-        <v>20773</v>
+        <v>17058</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Công tử đẹp trai quá [Dịch]</t>
+          <t>Bắt Đầu Vừa Vặn Cẩu Hết Mười Năm, Ta Vô Địch [Convert]</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -18304,15 +18304,15 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I389" t="n">
-        <v>0.3885</v>
+        <v>0.3328</v>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20773-cong-tu-dep-trai-qua-dich</t>
+          <t>https://sitruyencv.com/story/17058-bat-dau-vua-van-cau-het-muoi-nam-ta-vo-dich-convert</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -18336,29 +18336,29 @@
         <v>9</v>
       </c>
       <c r="E390" t="n">
-        <v>8979</v>
+        <v>20803</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>70 Quân Hôn Binh Vương Đầu Quả Tim Sủng [Convert]</t>
+          <t>Quỷ Đạo Tiên Lộ [Dịch]</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Tiên Hiệp, Linh Dị, Huyền Nghi Thần Quái</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I390" t="n">
-        <v>0.3878</v>
+        <v>0.3313</v>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8979-70-quan-hon-binh-vuong-dau-qua-tim-sung-convert</t>
+          <t>https://sitruyencv.com/story/20803-quy-dao-tien-lo-dich</t>
         </is>
       </c>
     </row>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Tìm truyện có phong cách thiết huyết</t>
+          <t>Tìm truyện có phong cách thiết huyết có ít hơn 1500 chương</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -18382,29 +18382,29 @@
         <v>10</v>
       </c>
       <c r="E391" t="n">
-        <v>20532</v>
+        <v>20776</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>Vai Ác: Bắt Đầu Đánh Mặt Chiến Thần, Nữ Tổng Giám Đốc Giúp Ta Xuất Khí [Dịch]</t>
+          <t>Vạn Tộc Chiến Trường: Ta Có Hệ Thống Bạo Kích Hàng Tỷ Lần [Dịch]</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Đô Thị, Hệ Thống, Xuyên Sách</t>
+          <t>Đô Thị, Võng Du, Hệ Thống</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I391" t="n">
-        <v>0.3849</v>
+        <v>0.3301</v>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20532-vai-ac-bat-dau-danh-mat-chien-than-nu-tong-giam-doc-giup-ta-xuat-khi-dich</t>
+          <t>https://sitruyencv.com/story/20776-van-toc-chien-truong-ta-co-he-thong-bao-kich-hang-ty-lan-dich</t>
         </is>
       </c>
     </row>
@@ -18416,7 +18416,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -18428,29 +18428,29 @@
         <v>1</v>
       </c>
       <c r="E392" t="n">
-        <v>20773</v>
+        <v>13674</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>Công tử đẹp trai quá [Dịch]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I392" t="n">
-        <v>0.4315</v>
+        <v>0.4272</v>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20773-cong-tu-dep-trai-qua-dich</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18462,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -18492,7 +18492,7 @@
         </is>
       </c>
       <c r="I393" t="n">
-        <v>0.4219</v>
+        <v>0.405</v>
       </c>
       <c r="J393" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -18520,11 +18520,11 @@
         <v>3</v>
       </c>
       <c r="E394" t="n">
-        <v>9820</v>
+        <v>14684</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
+          <t>Vô Địch Từ Miểu Sát Ức Vạn Thiên Phú Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
@@ -18538,11 +18538,11 @@
         </is>
       </c>
       <c r="I394" t="n">
-        <v>0.4204</v>
+        <v>0.4023</v>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/14684-vo-dich-tu-mieu-sat-uc-van-thien-phu-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -18554,7 +18554,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -18566,16 +18566,16 @@
         <v>4</v>
       </c>
       <c r="E395" t="n">
-        <v>18262</v>
+        <v>20773</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>Thần Bí Khôi Phục : Từ Quỷ Tranh Vẽ Bắt Đầu [Convert]</t>
+          <t>Công tử đẹp trai quá [Dịch]</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Huyền Nghi, Huyền Nghi Thần Quái</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -18584,11 +18584,11 @@
         </is>
       </c>
       <c r="I395" t="n">
-        <v>0.4168</v>
+        <v>0.3974</v>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18262-than-bi-khoi-phuc-tu-quy-tranh-ve-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/20773-cong-tu-dep-trai-qua-dich</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -18612,11 +18612,11 @@
         <v>5</v>
       </c>
       <c r="E396" t="n">
-        <v>13561</v>
+        <v>18885</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>Sau Khi Sống Lại Mới Phát Hiện, Ta Đúng Là Thiên Mệnh Nhân Vật Chính! [Convert]</t>
+          <t>Chiến Thần Cuồng Tiêu Chi Chư Thiên Vạn Giới [Convert]</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -18630,11 +18630,11 @@
         </is>
       </c>
       <c r="I396" t="n">
-        <v>0.4128</v>
+        <v>0.3951</v>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13561-sau-khi-song-lai-moi-phat-hien-ta-dung-la-thien-menh-nhan-vat-chinh-convert</t>
+          <t>https://sitruyencv.com/story/18885-chien-than-cuong-tieu-chi-chu-thien-van-gioi-convert</t>
         </is>
       </c>
     </row>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -18658,29 +18658,29 @@
         <v>6</v>
       </c>
       <c r="E397" t="n">
-        <v>2385</v>
+        <v>14198</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>Tối Cường Hệ Thống [Convert]</t>
+          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I397" t="n">
-        <v>0.4119</v>
+        <v>0.3908</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/2385-toi-cuong-he-thong-convert</t>
+          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -18704,16 +18704,16 @@
         <v>7</v>
       </c>
       <c r="E398" t="n">
-        <v>20259</v>
+        <v>8524</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>Một Xà Đắc Đạo [Dịch]</t>
+          <t>Mạt Thế Trọng Sinh: Tuyệt Sắc Pháo Hôi Đại Tiểu Thư Nghịch Tập [Convert]</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Điền Văn, Tiên Hiệp Kỳ Duyên, Huyền Nghi Thần Quái</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -18722,11 +18722,11 @@
         </is>
       </c>
       <c r="I398" t="n">
-        <v>0.4116</v>
+        <v>0.3887</v>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20259-mot-xa-dac-dao-dich</t>
+          <t>https://sitruyencv.com/story/8524-mat-the-trong-sinh-tuyet-sac-phao-hoi-dai-tieu-thu-nghich-tap-convert</t>
         </is>
       </c>
     </row>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -18750,16 +18750,16 @@
         <v>8</v>
       </c>
       <c r="E399" t="n">
-        <v>1063</v>
+        <v>15013</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>Cao Võ: Cháu Gái Bị Khi Phụ, 8 Tuổi Ta Chắn Cửa Trường! [Convert]</t>
+          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -18768,11 +18768,11 @@
         </is>
       </c>
       <c r="I399" t="n">
-        <v>0.4114</v>
+        <v>0.3881</v>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/1063-cao-vo-chau-gai-bi-khi-phu-8-tuoi-ta-chan-cua-truong-convert</t>
+          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
         </is>
       </c>
     </row>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -18796,29 +18796,29 @@
         <v>9</v>
       </c>
       <c r="E400" t="n">
-        <v>17533</v>
+        <v>2818</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>Vô Địch Theo Cướp Đoạt Khí Huyết Bắt Đầu [Convert]</t>
+          <t>Nghịch Thiên Tà Thần [Convert]</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I400" t="n">
-        <v>0.4083</v>
+        <v>0.3871</v>
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17533-vo-dich-theo-cuop-doat-khi-huyet-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/2818-nghich-thien-ta-than-convert</t>
         </is>
       </c>
     </row>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính là thiên tài</t>
+          <t>Tìm truyện có nhân vật chính là thiên tài có trạng thái đang ra và hơn 500 chương</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -18842,29 +18842,29 @@
         <v>10</v>
       </c>
       <c r="E401" t="n">
-        <v>14042</v>
+        <v>20259</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>Ông Trời Đền Bù Cho Người Cần Cù: Bắt Đầu Thông Gia Nghèo Túng Thiên Kim [Convert]</t>
+          <t>Một Xà Đắc Đạo [Dịch]</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp, Điền Văn, Tiên Hiệp Kỳ Duyên, Huyền Nghi Thần Quái</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I401" t="n">
-        <v>0.4073</v>
+        <v>0.387</v>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14042-ong-troi-den-bu-cho-nguoi-can-cu-bat-dau-thong-gia-ngheo-tung-thien-kim-convert</t>
+          <t>https://sitruyencv.com/story/20259-mot-xa-dac-dao-dich</t>
         </is>
       </c>
     </row>
@@ -28996,7 +28996,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -29008,11 +29008,11 @@
         <v>1</v>
       </c>
       <c r="E622" t="n">
-        <v>17365</v>
+        <v>16814</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Ta Có Một Gốc Thần Thoại Thụ [Convert]</t>
+          <t>Tuổi Già Bị Lão Bà Chia Tay, Hệ Thống Rốt Cuộc Đã Đến [Convert]</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -29022,15 +29022,15 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I622" t="n">
-        <v>0.399</v>
+        <v>0.4021</v>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17365-ta-co-mot-goc-than-thoai-thu-convert</t>
+          <t>https://sitruyencv.com/story/16814-tuoi-gia-bi-lao-ba-chia-tay-he-thong-rot-cuoc-da-den-convert</t>
         </is>
       </c>
     </row>
@@ -29042,7 +29042,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
@@ -29072,7 +29072,7 @@
         </is>
       </c>
       <c r="I623" t="n">
-        <v>0.3969</v>
+        <v>0.3982</v>
       </c>
       <c r="J623" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
@@ -29100,16 +29100,16 @@
         <v>3</v>
       </c>
       <c r="E624" t="n">
-        <v>18831</v>
+        <v>17365</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Hệ Thống Trừu Tượng, Ta Cũng Chẳng Kém Gì!!! [Dịch]</t>
+          <t>Ta Có Một Gốc Thần Thoại Thụ [Convert]</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>Đô Thị, Hệ Thống</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -29118,11 +29118,11 @@
         </is>
       </c>
       <c r="I624" t="n">
-        <v>0.3919</v>
+        <v>0.3982</v>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18831-he-thong-truu-tuong-ta-cung-chang-kem-gi-dich</t>
+          <t>https://sitruyencv.com/story/17365-ta-co-mot-goc-than-thoai-thu-convert</t>
         </is>
       </c>
     </row>
@@ -29134,7 +29134,7 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
@@ -29146,11 +29146,11 @@
         <v>4</v>
       </c>
       <c r="E625" t="n">
-        <v>18913</v>
+        <v>5138</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Khai Cục Xông Sư Nghịch Đồ, Thức Tỉnh Hệ Thống Kịch Bản Nhân Sinh [Convert]</t>
+          <t>Đánh Dấu Già Thiên Trăm Năm Thành Thánh [Convert]</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -29160,15 +29160,15 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I625" t="n">
-        <v>0.3865</v>
+        <v>0.3934</v>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18913-khai-cuc-xong-su-nghich-do-thuc-tinh-he-thong-kich-ban-nhan-sinh-convert</t>
+          <t>https://sitruyencv.com/story/5138-danh-dau-gia-thien-tram-nam-thanh-thanh-convert</t>
         </is>
       </c>
     </row>
@@ -29180,7 +29180,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
@@ -29192,29 +29192,29 @@
         <v>5</v>
       </c>
       <c r="E626" t="n">
-        <v>18853</v>
+        <v>19064</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Tây Du: Bắt Đầu Từ Công Chiếu Đại Thoại Tây Du [Dịch]</t>
+          <t>Hợp Hoan Tông, Từ Chăm Sóc Đạo Lữ Của Sư Đệ Bắt Đầu Tu Tiên [Dịch]</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Đồng Nhân, Hệ Thống</t>
+          <t>Huyền Huyễn, Hệ Thống, Phản Phái, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I626" t="n">
-        <v>0.3855</v>
+        <v>0.3826</v>
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18853-tay-du-bat-dau-tu-cong-chieu-dai-thoai-tay-du-dich</t>
+          <t>https://sitruyencv.com/story/19064-hop-hoan-tong-tu-cham-soc-dao-lu-cua-su-de-bat-dau-tu-tien-dich</t>
         </is>
       </c>
     </row>
@@ -29226,7 +29226,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C627" t="inlineStr">
@@ -29238,29 +29238,29 @@
         <v>6</v>
       </c>
       <c r="E627" t="n">
-        <v>20775</v>
+        <v>12094</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Tất Cả Theo Cẩm Y Vệ Bắt Đầu [Dịch]</t>
+          <t>Bắt Đầu Thanh Vân Tông Chủ, Triệu Hoán Đại Đế Cảnh Lão Tổ [Convert]</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Kiếm Hiệp, Hệ Thống, Huyền Nghi Thần Quái</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I627" t="n">
-        <v>0.3835</v>
+        <v>0.3797</v>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20775-tat-ca-theo-cam-y-ve-bat-dau-dich</t>
+          <t>https://sitruyencv.com/story/12094-bat-dau-thanh-van-tong-chu-trieu-hoan-dai-de-canh-lao-to-convert</t>
         </is>
       </c>
     </row>
@@ -29272,7 +29272,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C628" t="inlineStr">
@@ -29284,29 +29284,29 @@
         <v>7</v>
       </c>
       <c r="E628" t="n">
-        <v>19064</v>
+        <v>9820</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>Hợp Hoan Tông, Từ Chăm Sóc Đạo Lữ Của Sư Đệ Bắt Đầu Tu Tiên [Dịch]</t>
+          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>Huyền Huyễn, Hệ Thống, Phản Phái, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I628" t="n">
-        <v>0.3799</v>
+        <v>0.3764</v>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19064-hop-hoan-tong-tu-cham-soc-dao-lu-cua-su-de-bat-dau-tu-tien-dich</t>
+          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
         </is>
       </c>
     </row>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C629" t="inlineStr">
@@ -29348,7 +29348,7 @@
         </is>
       </c>
       <c r="I629" t="n">
-        <v>0.3743</v>
+        <v>0.374</v>
       </c>
       <c r="J629" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -29376,11 +29376,11 @@
         <v>9</v>
       </c>
       <c r="E630" t="n">
-        <v>16814</v>
+        <v>563</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>Tuổi Già Bị Lão Bà Chia Tay, Hệ Thống Rốt Cuộc Đã Đến [Convert]</t>
+          <t>Bế Quan 100. 000 Năm, Kỳ Lân Tộc Mời Ta Xuất Quan Làm Chủ [Convert]</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -29394,11 +29394,11 @@
         </is>
       </c>
       <c r="I630" t="n">
-        <v>0.3733</v>
+        <v>0.3731</v>
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16814-tuoi-gia-bi-lao-ba-chia-tay-he-thong-rot-cuoc-da-den-convert</t>
+          <t>https://sitruyencv.com/story/563-be-quan-100-000-nam-ky-lan-toc-moi-ta-xuat-quan-lam-chu-convert</t>
         </is>
       </c>
     </row>
@@ -29410,7 +29410,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống</t>
+          <t>Tìm truyện có yếu tố đông phương huyền huyễn và hệ thống có trạng thái hoàn thành</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -29422,11 +29422,11 @@
         <v>10</v>
       </c>
       <c r="E631" t="n">
-        <v>6637</v>
+        <v>17916</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Trùng Sinh Phối Hệ Thống, Ta Vô Địch Rất Hợp Lý A [Convert]</t>
+          <t>Từ Thiết Y Công Bắt Đầu Nhục Thân Thành Thánh [Convert]</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -29436,15 +29436,15 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I631" t="n">
-        <v>0.371</v>
+        <v>0.3724</v>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/6637-trung-sinh-phoi-he-thong-ta-vo-dich-rat-hop-ly-a-convert</t>
+          <t>https://sitruyencv.com/story/17916-tu-thiet-y-cong-bat-dau-nhuc-than-thanh-thanh-convert</t>
         </is>
       </c>
     </row>
@@ -29456,7 +29456,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
@@ -29468,16 +29468,16 @@
         <v>1</v>
       </c>
       <c r="E632" t="n">
-        <v>19064</v>
+        <v>13674</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>Hợp Hoan Tông, Từ Chăm Sóc Đạo Lữ Của Sư Đệ Bắt Đầu Tu Tiên [Dịch]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>Huyền Huyễn, Hệ Thống, Phản Phái, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -29486,11 +29486,11 @@
         </is>
       </c>
       <c r="I632" t="n">
-        <v>0.4498</v>
+        <v>0.41</v>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19064-hop-hoan-tong-tu-cham-soc-dao-lu-cua-su-de-bat-dau-tu-tien-dich</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -29502,7 +29502,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
@@ -29514,16 +29514,16 @@
         <v>2</v>
       </c>
       <c r="E633" t="n">
-        <v>19992</v>
+        <v>19064</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>Trường Sinh Tu Tiên, Từ Thục Năng Sinh Xảo Bắt Đầu [Convert]</t>
+          <t>Hợp Hoan Tông, Từ Chăm Sóc Đạo Lữ Của Sư Đệ Bắt Đầu Tu Tiên [Dịch]</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn, Hệ Thống, Phản Phái, Cổ Đại, Tiên Hiệp Kỳ Duyên, Cổ Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -29532,11 +29532,11 @@
         </is>
       </c>
       <c r="I633" t="n">
-        <v>0.4363</v>
+        <v>0.4098</v>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19992-truong-sinh-tu-tien-tu-thuc-nang-sinh-xao-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/19064-hop-hoan-tong-tu-cham-soc-dao-lu-cua-su-de-bat-dau-tu-tien-dich</t>
         </is>
       </c>
     </row>
@@ -29548,7 +29548,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C634" t="inlineStr">
@@ -29560,29 +29560,29 @@
         <v>3</v>
       </c>
       <c r="E634" t="n">
-        <v>9820</v>
+        <v>14198</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
+          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I634" t="n">
-        <v>0.432</v>
+        <v>0.4056</v>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
         </is>
       </c>
     </row>
@@ -29594,7 +29594,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C635" t="inlineStr">
@@ -29624,7 +29624,7 @@
         </is>
       </c>
       <c r="I635" t="n">
-        <v>0.4284</v>
+        <v>0.39</v>
       </c>
       <c r="J635" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C636" t="inlineStr">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="I636" t="n">
-        <v>0.4254</v>
+        <v>0.3885</v>
       </c>
       <c r="J636" t="inlineStr">
         <is>
@@ -29686,7 +29686,7 @@
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C637" t="inlineStr">
@@ -29698,16 +29698,16 @@
         <v>6</v>
       </c>
       <c r="E637" t="n">
-        <v>18831</v>
+        <v>11464</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>Hệ Thống Trừu Tượng, Ta Cũng Chẳng Kém Gì!!! [Dịch]</t>
+          <t>Vô Thượng Tiên! [Convert]</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>Đô Thị, Hệ Thống</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -29716,11 +29716,11 @@
         </is>
       </c>
       <c r="I637" t="n">
-        <v>0.4233</v>
+        <v>0.3861</v>
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18831-he-thong-truu-tuong-ta-cung-chang-kem-gi-dich</t>
+          <t>https://sitruyencv.com/story/11464-vo-thuong-tien-convert</t>
         </is>
       </c>
     </row>
@@ -29732,7 +29732,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -29744,16 +29744,16 @@
         <v>7</v>
       </c>
       <c r="E638" t="n">
-        <v>14198</v>
+        <v>19400</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Bảo Ngươi Khế Ước Linh Thú, Ngươi Lại Đi Khế Ước Tuyệt Mỹ Sư Tỷ? [Convert]</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -29762,11 +29762,11 @@
         </is>
       </c>
       <c r="I638" t="n">
-        <v>0.4227</v>
+        <v>0.3842</v>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/19400-bao-nguoi-khe-uoc-linh-thu-nguoi-lai-di-khe-uoc-tuyet-my-su-ty-convert</t>
         </is>
       </c>
     </row>
@@ -29778,7 +29778,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C639" t="inlineStr">
@@ -29790,11 +29790,11 @@
         <v>8</v>
       </c>
       <c r="E639" t="n">
-        <v>20773</v>
+        <v>9820</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>Công tử đẹp trai quá [Dịch]</t>
+          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -29808,11 +29808,11 @@
         </is>
       </c>
       <c r="I639" t="n">
-        <v>0.4202</v>
+        <v>0.3841</v>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20773-cong-tu-dep-trai-qua-dich</t>
+          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
         </is>
       </c>
     </row>
@@ -29824,7 +29824,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -29836,16 +29836,16 @@
         <v>9</v>
       </c>
       <c r="E640" t="n">
-        <v>18422</v>
+        <v>171</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Ta Nộp Hệ Thống Cho Lão Tổ, Vô Tình Biến Cả Gia Tộc Thành Tiên [Dịch]</t>
+          <t>Thời Trung Cổ Truyền Kỳ Thợ Săn Quỷ [Convert]</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống, Cổ Đại</t>
+          <t>Tây Phương Kỳ Huyễn</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -29854,11 +29854,11 @@
         </is>
       </c>
       <c r="I640" t="n">
-        <v>0.4168</v>
+        <v>0.3833</v>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18422-ta-nop-he-thong-cho-lao-to-vo-tinh-bien-ca-gia-toc-thanh-tien-dich</t>
+          <t>https://sitruyencv.com/story/171-thoi-trung-co-truyen-ky-tho-san-quy-convert</t>
         </is>
       </c>
     </row>
@@ -29870,7 +29870,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống</t>
+          <t>Tìm truyện có yếu tố huyễn tưởng tu tiên và hệ thống có hơn 500 chương truyện</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -29882,29 +29882,29 @@
         <v>10</v>
       </c>
       <c r="E641" t="n">
-        <v>171</v>
+        <v>15013</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>Thời Trung Cổ Truyền Kỳ Thợ Săn Quỷ [Convert]</t>
+          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
         <is>
-          <t>Tây Phương Kỳ Huyễn</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I641" t="n">
-        <v>0.4161</v>
+        <v>0.3802</v>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/171-thoi-trung-co-truyen-ky-tho-san-quy-convert</t>
+          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
         </is>
       </c>
     </row>
@@ -29916,7 +29916,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -29946,7 +29946,7 @@
         </is>
       </c>
       <c r="I642" t="n">
-        <v>0.4972</v>
+        <v>0.4838</v>
       </c>
       <c r="J642" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C643" t="inlineStr">
@@ -29974,16 +29974,16 @@
         <v>2</v>
       </c>
       <c r="E643" t="n">
-        <v>18913</v>
+        <v>13674</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Khai Cục Xông Sư Nghịch Đồ, Thức Tỉnh Hệ Thống Kịch Bản Nhân Sinh [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -29992,11 +29992,11 @@
         </is>
       </c>
       <c r="I643" t="n">
-        <v>0.481</v>
+        <v>0.4785</v>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18913-khai-cuc-xong-su-nghich-do-thuc-tinh-he-thong-kich-ban-nhan-sinh-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -30008,7 +30008,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -30020,16 +30020,16 @@
         <v>3</v>
       </c>
       <c r="E644" t="n">
-        <v>13674</v>
+        <v>12094</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
+          <t>Bắt Đầu Thanh Vân Tông Chủ, Triệu Hoán Đại Đế Cảnh Lão Tổ [Convert]</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -30038,11 +30038,11 @@
         </is>
       </c>
       <c r="I644" t="n">
-        <v>0.4803</v>
+        <v>0.4664</v>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
+          <t>https://sitruyencv.com/story/12094-bat-dau-thanh-van-tong-chu-trieu-hoan-dai-de-canh-lao-to-convert</t>
         </is>
       </c>
     </row>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -30066,16 +30066,16 @@
         <v>4</v>
       </c>
       <c r="E645" t="n">
-        <v>18422</v>
+        <v>18913</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>Ta Nộp Hệ Thống Cho Lão Tổ, Vô Tình Biến Cả Gia Tộc Thành Tiên [Dịch]</t>
+          <t>Khai Cục Xông Sư Nghịch Đồ, Thức Tỉnh Hệ Thống Kịch Bản Nhân Sinh [Convert]</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống, Cổ Đại</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -30084,11 +30084,11 @@
         </is>
       </c>
       <c r="I645" t="n">
-        <v>0.4598</v>
+        <v>0.4608</v>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18422-ta-nop-he-thong-cho-lao-to-vo-tinh-bien-ca-gia-toc-thanh-tien-dich</t>
+          <t>https://sitruyencv.com/story/18913-khai-cuc-xong-su-nghich-do-thuc-tinh-he-thong-kich-ban-nhan-sinh-convert</t>
         </is>
       </c>
     </row>
@@ -30100,7 +30100,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -30112,16 +30112,16 @@
         <v>5</v>
       </c>
       <c r="E646" t="n">
-        <v>12094</v>
+        <v>20776</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Bắt Đầu Thanh Vân Tông Chủ, Triệu Hoán Đại Đế Cảnh Lão Tổ [Convert]</t>
+          <t>Vạn Tộc Chiến Trường: Ta Có Hệ Thống Bạo Kích Hàng Tỷ Lần [Dịch]</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đô Thị, Võng Du, Hệ Thống</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -30130,11 +30130,11 @@
         </is>
       </c>
       <c r="I646" t="n">
-        <v>0.4567</v>
+        <v>0.4516</v>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12094-bat-dau-thanh-van-tong-chu-trieu-hoan-dai-de-canh-lao-to-convert</t>
+          <t>https://sitruyencv.com/story/20776-van-toc-chien-truong-ta-co-he-thong-bao-kich-hang-ty-lan-dich</t>
         </is>
       </c>
     </row>
@@ -30146,7 +30146,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
@@ -30158,29 +30158,29 @@
         <v>6</v>
       </c>
       <c r="E647" t="n">
-        <v>20772</v>
+        <v>13739</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Hệ Thống: Để Ngươi Giúp Đồ Đệ Mạnh Lên, Không Có Để Ngươi Vô Địch [Dịch]</t>
+          <t>Đa Tử Đa Phúc, Bắt Đầu Liền Đưa Tuyệt Mỹ Lão Bà [Convert]</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I647" t="n">
-        <v>0.4511</v>
+        <v>0.4475</v>
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20772-he-thong-de-nguoi-giup-do-de-manh-len-khong-co-de-nguoi-vo-dich-dich</t>
+          <t>https://sitruyencv.com/story/13739-da-tu-da-phuc-bat-dau-lien-dua-tuyet-my-lao-ba-convert</t>
         </is>
       </c>
     </row>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -30204,29 +30204,29 @@
         <v>7</v>
       </c>
       <c r="E648" t="n">
-        <v>18831</v>
+        <v>5138</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>Hệ Thống Trừu Tượng, Ta Cũng Chẳng Kém Gì!!! [Dịch]</t>
+          <t>Đánh Dấu Già Thiên Trăm Năm Thành Thánh [Convert]</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>Đô Thị, Hệ Thống</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I648" t="n">
-        <v>0.45</v>
+        <v>0.4442</v>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18831-he-thong-truu-tuong-ta-cung-chang-kem-gi-dich</t>
+          <t>https://sitruyencv.com/story/5138-danh-dau-gia-thien-tram-nam-thanh-thanh-convert</t>
         </is>
       </c>
     </row>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -30250,29 +30250,29 @@
         <v>8</v>
       </c>
       <c r="E649" t="n">
-        <v>13739</v>
+        <v>14684</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>Đa Tử Đa Phúc, Bắt Đầu Liền Đưa Tuyệt Mỹ Lão Bà [Convert]</t>
+          <t>Vô Địch Từ Miểu Sát Ức Vạn Thiên Phú Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>Dã Sử</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I649" t="n">
-        <v>0.4482</v>
+        <v>0.4401</v>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13739-da-tu-da-phuc-bat-dau-lien-dua-tuyet-my-lao-ba-convert</t>
+          <t>https://sitruyencv.com/story/14684-vo-dich-tu-mieu-sat-uc-van-thien-phu-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -30284,7 +30284,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -30296,29 +30296,29 @@
         <v>9</v>
       </c>
       <c r="E650" t="n">
-        <v>6637</v>
+        <v>14198</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Trùng Sinh Phối Hệ Thống, Ta Vô Địch Rất Hợp Lý A [Convert]</t>
+          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I650" t="n">
-        <v>0.4412</v>
+        <v>0.4393</v>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/6637-trung-sinh-phoi-he-thong-ta-vo-dich-rat-hop-ly-a-convert</t>
+          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
         </is>
       </c>
     </row>
@@ -30330,7 +30330,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống</t>
+          <t>Tìm truyện có yếu tố chư thiên vạn giới và hệ thống có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -30342,29 +30342,29 @@
         <v>10</v>
       </c>
       <c r="E651" t="n">
-        <v>20776</v>
+        <v>15013</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Vạn Tộc Chiến Trường: Ta Có Hệ Thống Bạo Kích Hàng Tỷ Lần [Dịch]</t>
+          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Đô Thị, Võng Du, Hệ Thống</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I651" t="n">
-        <v>0.4362</v>
+        <v>0.4391</v>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20776-van-toc-chien-truong-ta-co-he-thong-bao-kich-hang-ty-lan-dich</t>
+          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
         </is>
       </c>
     </row>
@@ -38196,7 +38196,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -38208,29 +38208,29 @@
         <v>1</v>
       </c>
       <c r="E822" t="n">
-        <v>10623</v>
+        <v>13674</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
-          <t>Đấu Phá: Đa Tử Đa Phúc, Ta Chế Tạo Mạnh Nhất Gia Tộc [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G822" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I822" t="n">
-        <v>0.4799</v>
+        <v>0.461</v>
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/10623-dau-pha-da-tu-da-phuc-ta-che-tao-manh-nhat-gia-toc-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -38242,7 +38242,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -38254,29 +38254,29 @@
         <v>2</v>
       </c>
       <c r="E823" t="n">
-        <v>13674</v>
+        <v>8524</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
+          <t>Mạt Thế Trọng Sinh: Tuyệt Sắc Pháo Hôi Đại Tiểu Thư Nghịch Tập [Convert]</t>
         </is>
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Hiện Đại Ngôn Tình</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I823" t="n">
-        <v>0.4722</v>
+        <v>0.4532</v>
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
+          <t>https://sitruyencv.com/story/8524-mat-the-trong-sinh-tuyet-sac-phao-hoi-dai-tieu-thu-nghich-tap-convert</t>
         </is>
       </c>
     </row>
@@ -38288,7 +38288,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -38300,29 +38300,29 @@
         <v>3</v>
       </c>
       <c r="E824" t="n">
-        <v>6637</v>
+        <v>14198</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
-          <t>Trùng Sinh Phối Hệ Thống, Ta Vô Địch Rất Hợp Lý A [Convert]</t>
+          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
         </is>
       </c>
       <c r="G824" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I824" t="n">
-        <v>0.4523</v>
+        <v>0.4521</v>
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/6637-trung-sinh-phoi-he-thong-ta-vo-dich-rat-hop-ly-a-convert</t>
+          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
         </is>
       </c>
     </row>
@@ -38334,7 +38334,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -38346,16 +38346,16 @@
         <v>4</v>
       </c>
       <c r="E825" t="n">
-        <v>2385</v>
+        <v>10623</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>Tối Cường Hệ Thống [Convert]</t>
+          <t>Đấu Phá: Đa Tử Đa Phúc, Ta Chế Tạo Mạnh Nhất Gia Tộc [Convert]</t>
         </is>
       </c>
       <c r="G825" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H825" t="inlineStr">
@@ -38364,11 +38364,11 @@
         </is>
       </c>
       <c r="I825" t="n">
-        <v>0.4511</v>
+        <v>0.444</v>
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/2385-toi-cuong-he-thong-convert</t>
+          <t>https://sitruyencv.com/story/10623-dau-pha-da-tu-da-phuc-ta-che-tao-manh-nhat-gia-toc-convert</t>
         </is>
       </c>
     </row>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -38392,29 +38392,29 @@
         <v>5</v>
       </c>
       <c r="E826" t="n">
-        <v>16100</v>
+        <v>14684</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Cao Võ: Ta Có Thể Hấp Thu Điểm Kinh Nghiệm [Convert]</t>
+          <t>Vô Địch Từ Miểu Sát Ức Vạn Thiên Phú Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="G826" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I826" t="n">
-        <v>0.4446</v>
+        <v>0.432</v>
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16100-cao-vo-ta-co-the-hap-thu-diem-kinh-nghiem-convert</t>
+          <t>https://sitruyencv.com/story/14684-vo-dich-tu-mieu-sat-uc-van-thien-phu-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -38426,7 +38426,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -38438,16 +38438,16 @@
         <v>6</v>
       </c>
       <c r="E827" t="n">
-        <v>14198</v>
+        <v>19472</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>Vừa Thành Phong Hào Đấu La, Đạo Lữ Hệ Thống Tìm Tới Cửa! [Convert]</t>
+          <t>Đại Minh: Bắt Đầu Cứu Người Đáng Giết [Convert]</t>
         </is>
       </c>
       <c r="G827" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="H827" t="inlineStr">
@@ -38456,11 +38456,11 @@
         </is>
       </c>
       <c r="I827" t="n">
-        <v>0.4444</v>
+        <v>0.4288</v>
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14198-vua-thanh-phong-hao-dau-la-dao-lu-he-thong-tim-toi-cua-convert</t>
+          <t>https://sitruyencv.com/story/19472-dai-minh-bat-dau-cuu-nguoi-dang-giet-convert</t>
         </is>
       </c>
     </row>
@@ -38472,7 +38472,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -38484,29 +38484,29 @@
         <v>7</v>
       </c>
       <c r="E828" t="n">
-        <v>18422</v>
+        <v>19019</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>Ta Nộp Hệ Thống Cho Lão Tổ, Vô Tình Biến Cả Gia Tộc Thành Tiên [Dịch]</t>
+          <t>Thần Tuyển Lạc Viên [Dịch]</t>
         </is>
       </c>
       <c r="G828" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống, Cổ Đại</t>
+          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
         </is>
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I828" t="n">
-        <v>0.4424</v>
+        <v>0.4274</v>
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18422-ta-nop-he-thong-cho-lao-to-vo-tinh-bien-ca-gia-toc-thanh-tien-dich</t>
+          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
         </is>
       </c>
     </row>
@@ -38518,7 +38518,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -38548,7 +38548,7 @@
         </is>
       </c>
       <c r="I829" t="n">
-        <v>0.4422</v>
+        <v>0.416</v>
       </c>
       <c r="J829" t="inlineStr">
         <is>
@@ -38564,7 +38564,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -38576,16 +38576,16 @@
         <v>9</v>
       </c>
       <c r="E830" t="n">
-        <v>8524</v>
+        <v>14711</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>Mạt Thế Trọng Sinh: Tuyệt Sắc Pháo Hôi Đại Tiểu Thư Nghịch Tập [Convert]</t>
+          <t>Vô Hạn Thăng Cấp: Lại Tăng Cấp Liền Muốn Cưới Nữ Ma Đầu [Convert]</t>
         </is>
       </c>
       <c r="G830" t="inlineStr">
         <is>
-          <t>Hiện Đại Ngôn Tình</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H830" t="inlineStr">
@@ -38594,11 +38594,11 @@
         </is>
       </c>
       <c r="I830" t="n">
-        <v>0.4422</v>
+        <v>0.4148</v>
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/8524-mat-the-trong-sinh-tuyet-sac-phao-hoi-dai-tieu-thu-nghich-tap-convert</t>
+          <t>https://sitruyencv.com/story/14711-vo-han-thang-cap-lai-tang-cap-lien-muon-cuoi-nu-ma-dau-convert</t>
         </is>
       </c>
     </row>
@@ -38610,7 +38610,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực và main cơ trí.</t>
+          <t>Tìm truyện mà vừa có hệ thống vừa phát triển thế lực, main cơ trí và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -38622,16 +38622,16 @@
         <v>10</v>
       </c>
       <c r="E831" t="n">
-        <v>19472</v>
+        <v>12225</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
-          <t>Đại Minh: Bắt Đầu Cứu Người Đáng Giết [Convert]</t>
+          <t>Bắt Đầu Bị Quăng, Ta Quay Người Trở Thành Ức Vạn Phú Ông [Convert]</t>
         </is>
       </c>
       <c r="G831" t="inlineStr">
         <is>
-          <t>Dã Sử</t>
+          <t>Đô Thị</t>
         </is>
       </c>
       <c r="H831" t="inlineStr">
@@ -38640,11 +38640,11 @@
         </is>
       </c>
       <c r="I831" t="n">
-        <v>0.4394</v>
+        <v>0.4144</v>
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19472-dai-minh-bat-dau-cuu-nguoi-dang-giet-convert</t>
+          <t>https://sitruyencv.com/story/12225-bat-dau-bi-quang-ta-quay-nguoi-tro-thanh-uc-van-phu-ong-convert</t>
         </is>
       </c>
     </row>
@@ -39116,7 +39116,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -39146,7 +39146,7 @@
         </is>
       </c>
       <c r="I842" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4911</v>
       </c>
       <c r="J842" t="inlineStr">
         <is>
@@ -39162,7 +39162,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -39174,11 +39174,11 @@
         <v>2</v>
       </c>
       <c r="E843" t="n">
-        <v>14073</v>
+        <v>16388</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>One Piece: Ta Đã Nứt Ra, Nhưng Biến Dị Thiên Phú Siêu Cường [Convert]</t>
+          <t>Konoha Người Sưu Tập, Bắt Đầu Thu Được Uzumaki Tiên Nhân Thể [Convert]</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
@@ -39188,15 +39188,15 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I843" t="n">
-        <v>0.4938</v>
+        <v>0.4764</v>
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14073-one-piece-ta-da-nut-ra-nhung-bien-di-thien-phu-sieu-cuong-convert</t>
+          <t>https://sitruyencv.com/story/16388-konoha-nguoi-suu-tap-bat-dau-thu-duoc-uzumaki-tien-nhan-the-convert</t>
         </is>
       </c>
     </row>
@@ -39208,7 +39208,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -39220,29 +39220,29 @@
         <v>3</v>
       </c>
       <c r="E844" t="n">
-        <v>16388</v>
+        <v>13674</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>Konoha Người Sưu Tập, Bắt Đầu Thu Được Uzumaki Tiên Nhân Thể [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>Đồng Nhân</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I844" t="n">
-        <v>0.4774</v>
+        <v>0.4734</v>
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16388-konoha-nguoi-suu-tap-bat-dau-thu-duoc-uzumaki-tien-nhan-the-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -39254,7 +39254,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -39284,7 +39284,7 @@
         </is>
       </c>
       <c r="I845" t="n">
-        <v>0.4672</v>
+        <v>0.4632</v>
       </c>
       <c r="J845" t="inlineStr">
         <is>
@@ -39300,7 +39300,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -39312,16 +39312,16 @@
         <v>5</v>
       </c>
       <c r="E846" t="n">
-        <v>20479</v>
+        <v>20043</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>Ta, Konoha Thôn Đệ Nhất Ác Tặc [Dịch]</t>
+          <t>Giải Trí: Cùng Các Minh Tinh Sin Tồn Trên Hoang Đảo [Dịch]</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
         <is>
-          <t>Đồng Nhân, Hệ Thống, Xuyên Sách</t>
+          <t>Đô Thị, Kỳ Ảo, Hệ Thống, Tây Phương Kỳ Huyễn, Biến Thân, Điền Văn, Ngôn Tình, Nữ Phụ, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
         </is>
       </c>
       <c r="H846" t="inlineStr">
@@ -39330,11 +39330,11 @@
         </is>
       </c>
       <c r="I846" t="n">
-        <v>0.4606</v>
+        <v>0.4545</v>
       </c>
       <c r="J846" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20479-ta-konoha-thon-de-nhat-ac-tac-dich</t>
+          <t>https://sitruyencv.com/story/20043-giai-tri-cung-cac-minh-tinh-sin-ton-tren-hoang-dao-dich</t>
         </is>
       </c>
     </row>
@@ -39346,7 +39346,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -39358,29 +39358,29 @@
         <v>6</v>
       </c>
       <c r="E847" t="n">
-        <v>20043</v>
+        <v>14073</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>Giải Trí: Cùng Các Minh Tinh Sin Tồn Trên Hoang Đảo [Dịch]</t>
+          <t>One Piece: Ta Đã Nứt Ra, Nhưng Biến Dị Thiên Phú Siêu Cường [Convert]</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Đô Thị, Kỳ Ảo, Hệ Thống, Tây Phương Kỳ Huyễn, Biến Thân, Điền Văn, Ngôn Tình, Nữ Phụ, Hiện Đại Ngôn Tình, Lãng Mạn Thanh Xuân</t>
+          <t>Đồng Nhân</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I847" t="n">
-        <v>0.4447</v>
+        <v>0.4507</v>
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20043-giai-tri-cung-cac-minh-tinh-sin-ton-tren-hoang-dao-dich</t>
+          <t>https://sitruyencv.com/story/14073-one-piece-ta-da-nut-ra-nhung-bien-di-thien-phu-sieu-cuong-convert</t>
         </is>
       </c>
     </row>
@@ -39392,7 +39392,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -39404,29 +39404,29 @@
         <v>7</v>
       </c>
       <c r="E848" t="n">
-        <v>20022</v>
+        <v>20479</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>Người Ở Hợp Hoan Tông, Bắt Đầu Trở Thành Đạo Lữ Thánh Nữ! [Convert]</t>
+          <t>Ta, Konoha Thôn Đệ Nhất Ác Tặc [Dịch]</t>
         </is>
       </c>
       <c r="G848" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Đồng Nhân, Hệ Thống, Xuyên Sách</t>
         </is>
       </c>
       <c r="H848" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I848" t="n">
-        <v>0.4388</v>
+        <v>0.4466</v>
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20022-nguoi-o-hop-hoan-tong-bat-dau-tro-thanh-dao-lu-thanh-nu-convert</t>
+          <t>https://sitruyencv.com/story/20479-ta-konoha-thon-de-nhat-ac-tac-dich</t>
         </is>
       </c>
     </row>
@@ -39438,7 +39438,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -39450,29 +39450,29 @@
         <v>8</v>
       </c>
       <c r="E849" t="n">
-        <v>19613</v>
+        <v>19019</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>Đặc Nhiếp: Mị Ma Chính Thái, Đụng Đổ Mẹ Của Tiểu Nhượng [Dịch]</t>
+          <t>Thần Tuyển Lạc Viên [Dịch]</t>
         </is>
       </c>
       <c r="G849" t="inlineStr">
         <is>
-          <t>Huyền Huyễn, Đồng Nhân, Light Novel, Hệ Thống, Biến Thân, Xuyên Sách, Dị Năng, Sủng</t>
+          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
         </is>
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I849" t="n">
-        <v>0.4387</v>
+        <v>0.4454</v>
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19613-dac-nhiep-mi-ma-chinh-thai-dung-do-me-cua-tieu-nhuong-dich</t>
+          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
         </is>
       </c>
     </row>
@@ -39484,7 +39484,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -39496,29 +39496,29 @@
         <v>9</v>
       </c>
       <c r="E850" t="n">
-        <v>18422</v>
+        <v>15013</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>Ta Nộp Hệ Thống Cho Lão Tổ, Vô Tình Biến Cả Gia Tộc Thành Tiên [Dịch]</t>
+          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
         </is>
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống, Cổ Đại</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I850" t="n">
-        <v>0.4378</v>
+        <v>0.4416</v>
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18422-ta-nop-he-thong-cho-lao-to-vo-tinh-bien-ca-gia-toc-thanh-tien-dich</t>
+          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
         </is>
       </c>
     </row>
@@ -39530,7 +39530,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa</t>
+          <t>Hãy đề cử tôi truyện đồng nhân liên quan đến hải tặc hoặc là ninja, main có hệ thống phụ trợ càng tốt, đa tử đa phúc nữa có hơn 200 chương nha</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -39542,29 +39542,29 @@
         <v>10</v>
       </c>
       <c r="E851" t="n">
-        <v>19019</v>
+        <v>20022</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>Thần Tuyển Lạc Viên [Dịch]</t>
+          <t>Người Ở Hợp Hoan Tông, Bắt Đầu Trở Thành Đạo Lữ Thánh Nữ! [Convert]</t>
         </is>
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>Đô Thị, Võng Du, Hệ Thống, Dị Năng</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I851" t="n">
-        <v>0.4349</v>
+        <v>0.4409</v>
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19019-than-tuyen-lac-vien-dich</t>
+          <t>https://sitruyencv.com/story/20022-nguoi-o-hop-hoan-tong-bat-dau-tro-thanh-dao-lu-thanh-nu-convert</t>
         </is>
       </c>
     </row>
@@ -44636,7 +44636,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C962" t="inlineStr">
@@ -44648,11 +44648,11 @@
         <v>1</v>
       </c>
       <c r="E962" t="n">
-        <v>9820</v>
+        <v>14684</v>
       </c>
       <c r="F962" t="inlineStr">
         <is>
-          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
+          <t>Vô Địch Từ Miểu Sát Ức Vạn Thiên Phú Bắt Đầu [Convert]</t>
         </is>
       </c>
       <c r="G962" t="inlineStr">
@@ -44666,11 +44666,11 @@
         </is>
       </c>
       <c r="I962" t="n">
-        <v>0.4347</v>
+        <v>0.4812</v>
       </c>
       <c r="J962" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
+          <t>https://sitruyencv.com/story/14684-vo-dich-tu-mieu-sat-uc-van-thien-phu-bat-dau-convert</t>
         </is>
       </c>
     </row>
@@ -44682,7 +44682,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C963" t="inlineStr">
@@ -44694,11 +44694,11 @@
         <v>2</v>
       </c>
       <c r="E963" t="n">
-        <v>14684</v>
+        <v>15013</v>
       </c>
       <c r="F963" t="inlineStr">
         <is>
-          <t>Vô Địch Từ Miểu Sát Ức Vạn Thiên Phú Bắt Đầu [Convert]</t>
+          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
         </is>
       </c>
       <c r="G963" t="inlineStr">
@@ -44712,11 +44712,11 @@
         </is>
       </c>
       <c r="I963" t="n">
-        <v>0.4307</v>
+        <v>0.4558</v>
       </c>
       <c r="J963" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/14684-vo-dich-tu-mieu-sat-uc-van-thien-phu-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
         </is>
       </c>
     </row>
@@ -44728,7 +44728,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C964" t="inlineStr">
@@ -44740,11 +44740,11 @@
         <v>3</v>
       </c>
       <c r="E964" t="n">
-        <v>15013</v>
+        <v>9820</v>
       </c>
       <c r="F964" t="inlineStr">
         <is>
-          <t>Bắt Đầu: Ta Có Trọng Đồng Tiên Cốt Hỗn Độn Đạo Thể [Convert]</t>
+          <t>Bắt Đầu Mười Liên Rút Sau Đó Vô Địch [Convert]</t>
         </is>
       </c>
       <c r="G964" t="inlineStr">
@@ -44758,11 +44758,11 @@
         </is>
       </c>
       <c r="I964" t="n">
-        <v>0.4267</v>
+        <v>0.447</v>
       </c>
       <c r="J964" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/15013-bat-dau-ta-co-trong-dong-tien-cot-hon-don-dao-the-convert</t>
+          <t>https://sitruyencv.com/story/9820-bat-dau-muoi-lien-rut-sau-do-vo-dich-convert</t>
         </is>
       </c>
     </row>
@@ -44774,7 +44774,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C965" t="inlineStr">
@@ -44786,29 +44786,29 @@
         <v>4</v>
       </c>
       <c r="E965" t="n">
-        <v>16537</v>
+        <v>20472</v>
       </c>
       <c r="F965" t="inlineStr">
         <is>
-          <t>Tống Võ: Đại Tần Hoàng Tử, Các Ngươi Tu Võ Ta Tu Tiên [Convert]</t>
+          <t>Song Tu Vô Địch, Ta – Nghịch Thiên Võ Thần! [Dịch]</t>
         </is>
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H965" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I965" t="n">
-        <v>0.4191</v>
+        <v>0.4248</v>
       </c>
       <c r="J965" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16537-tong-vo-dai-tan-hoang-tu-cac-nguoi-tu-vo-ta-tu-tien-convert</t>
+          <t>https://sitruyencv.com/story/20472-song-tu-vo-dich-ta-nghich-thien-vo-than-dich</t>
         </is>
       </c>
     </row>
@@ -44820,7 +44820,7 @@
       </c>
       <c r="B966" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C966" t="inlineStr">
@@ -44832,29 +44832,29 @@
         <v>5</v>
       </c>
       <c r="E966" t="n">
-        <v>17533</v>
+        <v>13739</v>
       </c>
       <c r="F966" t="inlineStr">
         <is>
-          <t>Vô Địch Theo Cướp Đoạt Khí Huyết Bắt Đầu [Convert]</t>
+          <t>Đa Tử Đa Phúc, Bắt Đầu Liền Đưa Tuyệt Mỹ Lão Bà [Convert]</t>
         </is>
       </c>
       <c r="G966" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="H966" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I966" t="n">
-        <v>0.4168</v>
+        <v>0.4237</v>
       </c>
       <c r="J966" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17533-vo-dich-theo-cuop-doat-khi-huyet-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/13739-da-tu-da-phuc-bat-dau-lien-dua-tuyet-my-lao-ba-convert</t>
         </is>
       </c>
     </row>
@@ -44866,7 +44866,7 @@
       </c>
       <c r="B967" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C967" t="inlineStr">
@@ -44878,29 +44878,29 @@
         <v>6</v>
       </c>
       <c r="E967" t="n">
-        <v>20479</v>
+        <v>18831</v>
       </c>
       <c r="F967" t="inlineStr">
         <is>
-          <t>Ta, Konoha Thôn Đệ Nhất Ác Tặc [Dịch]</t>
+          <t>Hệ Thống Trừu Tượng, Ta Cũng Chẳng Kém Gì!!! [Dịch]</t>
         </is>
       </c>
       <c r="G967" t="inlineStr">
         <is>
-          <t>Đồng Nhân, Hệ Thống, Xuyên Sách</t>
+          <t>Đô Thị, Hệ Thống</t>
         </is>
       </c>
       <c r="H967" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I967" t="n">
-        <v>0.4155</v>
+        <v>0.4222</v>
       </c>
       <c r="J967" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20479-ta-konoha-thon-de-nhat-ac-tac-dich</t>
+          <t>https://sitruyencv.com/story/18831-he-thong-truu-tuong-ta-cung-chang-kem-gi-dich</t>
         </is>
       </c>
     </row>
@@ -44912,7 +44912,7 @@
       </c>
       <c r="B968" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C968" t="inlineStr">
@@ -44924,29 +44924,29 @@
         <v>7</v>
       </c>
       <c r="E968" t="n">
-        <v>16145</v>
+        <v>6637</v>
       </c>
       <c r="F968" t="inlineStr">
         <is>
-          <t>Liếm Cẩu Phản Diện Chỉ Nghĩ Cẩu , Nữ Chính Không Theo Sáo Lộ Đi [Convert]</t>
+          <t>Trùng Sinh Phối Hệ Thống, Ta Vô Địch Rất Hợp Lý A [Convert]</t>
         </is>
       </c>
       <c r="G968" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H968" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I968" t="n">
-        <v>0.4147</v>
+        <v>0.4175</v>
       </c>
       <c r="J968" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16145-liem-cau-phan-dien-chi-nghi-cau-nu-chinh-khong-theo-sao-lo-di-convert</t>
+          <t>https://sitruyencv.com/story/6637-trung-sinh-phoi-he-thong-ta-vo-dich-rat-hop-ly-a-convert</t>
         </is>
       </c>
     </row>
@@ -44958,7 +44958,7 @@
       </c>
       <c r="B969" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C969" t="inlineStr">
@@ -44970,29 +44970,29 @@
         <v>8</v>
       </c>
       <c r="E969" t="n">
-        <v>19729</v>
+        <v>18885</v>
       </c>
       <c r="F969" t="inlineStr">
         <is>
-          <t>Đấu La: Thu Phục Nữ Thần [Dịch]</t>
+          <t>Chiến Thần Cuồng Tiêu Chi Chư Thiên Vạn Giới [Convert]</t>
         </is>
       </c>
       <c r="G969" t="inlineStr">
         <is>
-          <t>Huyền Huyễn, Đồng Nhân, Hệ Thống, Phản Phái, Dị Giới, Sủng</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H969" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I969" t="n">
-        <v>0.4082</v>
+        <v>0.4141</v>
       </c>
       <c r="J969" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19729-dau-la-thu-phuc-nu-than-dich</t>
+          <t>https://sitruyencv.com/story/18885-chien-than-cuong-tieu-chi-chu-thien-van-gioi-convert</t>
         </is>
       </c>
     </row>
@@ -45004,7 +45004,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C970" t="inlineStr">
@@ -45016,29 +45016,29 @@
         <v>9</v>
       </c>
       <c r="E970" t="n">
-        <v>6637</v>
+        <v>16537</v>
       </c>
       <c r="F970" t="inlineStr">
         <is>
-          <t>Trùng Sinh Phối Hệ Thống, Ta Vô Địch Rất Hợp Lý A [Convert]</t>
+          <t>Tống Võ: Đại Tần Hoàng Tử, Các Ngươi Tu Võ Ta Tu Tiên [Convert]</t>
         </is>
       </c>
       <c r="G970" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H970" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I970" t="n">
-        <v>0.4082</v>
+        <v>0.4128</v>
       </c>
       <c r="J970" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/6637-trung-sinh-phoi-he-thong-ta-vo-dich-rat-hop-ly-a-convert</t>
+          <t>https://sitruyencv.com/story/16537-tong-vo-dai-tan-hoang-tu-cac-nguoi-tu-vo-ta-tu-tien-convert</t>
         </is>
       </c>
     </row>
@@ -45050,7 +45050,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống</t>
+          <t>Tìm truyện có nhân vật chính vô địch nhưng không có hệ thống và có trạng thái đang ra</t>
         </is>
       </c>
       <c r="C971" t="inlineStr">
@@ -45062,29 +45062,29 @@
         <v>10</v>
       </c>
       <c r="E971" t="n">
-        <v>20472</v>
+        <v>18959</v>
       </c>
       <c r="F971" t="inlineStr">
         <is>
-          <t>Song Tu Vô Địch, Ta – Nghịch Thiên Võ Thần! [Dịch]</t>
+          <t>Ta Thiên Đình Thái Tử Gia, Thiên Đế Cha Vô Địch, Ta Nằm [Convert]</t>
         </is>
       </c>
       <c r="G971" t="inlineStr">
         <is>
-          <t>Huyền Huyễn</t>
+          <t>Tiên Hiệp, Huyền Huyễn, Hệ Thống</t>
         </is>
       </c>
       <c r="H971" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I971" t="n">
-        <v>0.4062</v>
+        <v>0.4106</v>
       </c>
       <c r="J971" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20472-song-tu-vo-dich-ta-nghich-thien-vo-than-dich</t>
+          <t>https://sitruyencv.com/story/18959-ta-thien-dinh-thai-tu-gia-thien-de-cha-vo-dich-ta-nam-convert</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45096,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C972" t="inlineStr">
@@ -45126,7 +45126,7 @@
         </is>
       </c>
       <c r="I972" t="n">
-        <v>0.4249</v>
+        <v>0.41</v>
       </c>
       <c r="J972" t="inlineStr">
         <is>
@@ -45142,7 +45142,7 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C973" t="inlineStr">
@@ -45154,29 +45154,29 @@
         <v>2</v>
       </c>
       <c r="E973" t="n">
-        <v>2021</v>
+        <v>13674</v>
       </c>
       <c r="F973" t="inlineStr">
         <is>
-          <t>Dựa Vào Làm Ruộng Đi Lên Đỉnh Cao Nhân Sinh [Convert]</t>
+          <t>Vạn Thú Thế Gia Quật Khởi [Convert]</t>
         </is>
       </c>
       <c r="G973" t="inlineStr">
         <is>
-          <t>Cổ Đại Ngôn Tình</t>
+          <t>Tiên Hiệp</t>
         </is>
       </c>
       <c r="H973" t="inlineStr">
         <is>
-          <t>Hoàn thành</t>
+          <t>Đang ra</t>
         </is>
       </c>
       <c r="I973" t="n">
-        <v>0.4045</v>
+        <v>0.401</v>
       </c>
       <c r="J973" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/2021-dua-vao-lam-ruong-di-len-dinh-cao-nhan-sinh-convert</t>
+          <t>https://sitruyencv.com/story/13674-van-thu-the-gia-quat-khoi-convert</t>
         </is>
       </c>
     </row>
@@ -45188,7 +45188,7 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C974" t="inlineStr">
@@ -45200,16 +45200,16 @@
         <v>3</v>
       </c>
       <c r="E974" t="n">
-        <v>12662</v>
+        <v>16217</v>
       </c>
       <c r="F974" t="inlineStr">
         <is>
-          <t>Theo Nuốt Riêng Ngàn Vạn Ức Liếm Cẩu Kim Bắt Đầu Làm Thần Hào [Convert]</t>
+          <t>Tam Quốc Thần Thoại Thế Giới [Convert]</t>
         </is>
       </c>
       <c r="G974" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Võng Du</t>
         </is>
       </c>
       <c r="H974" t="inlineStr">
@@ -45218,11 +45218,11 @@
         </is>
       </c>
       <c r="I974" t="n">
-        <v>0.3962</v>
+        <v>0.3908</v>
       </c>
       <c r="J974" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12662-theo-nuot-rieng-ngan-van-uc-liem-cau-kim-bat-dau-lam-than-hao-convert</t>
+          <t>https://sitruyencv.com/story/16217-tam-quoc-than-thoai-the-gioi-convert</t>
         </is>
       </c>
     </row>
@@ -45234,7 +45234,7 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C975" t="inlineStr">
@@ -45246,16 +45246,16 @@
         <v>4</v>
       </c>
       <c r="E975" t="n">
-        <v>19521</v>
+        <v>20353</v>
       </c>
       <c r="F975" t="inlineStr">
         <is>
-          <t>Đại Minh Đã Mất, Ngươi Bảo Ta Nhậm Chức Cẩm Y Vệ? [Convert]</t>
+          <t>Từ Gia Phả Bắt Đầu Xây Dựng Trường Sinh Thế Gia [Dịch]</t>
         </is>
       </c>
       <c r="G975" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn, Điền Văn</t>
         </is>
       </c>
       <c r="H975" t="inlineStr">
@@ -45264,11 +45264,11 @@
         </is>
       </c>
       <c r="I975" t="n">
-        <v>0.3943</v>
+        <v>0.3747</v>
       </c>
       <c r="J975" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19521-dai-minh-da-mat-nguoi-bao-ta-nham-chuc-cam-y-ve-convert</t>
+          <t>https://sitruyencv.com/story/20353-tu-gia-pha-bat-dau-xay-dung-truong-sinh-the-gia-dich</t>
         </is>
       </c>
     </row>
@@ -45280,7 +45280,7 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C976" t="inlineStr">
@@ -45292,11 +45292,11 @@
         <v>5</v>
       </c>
       <c r="E976" t="n">
-        <v>16145</v>
+        <v>12662</v>
       </c>
       <c r="F976" t="inlineStr">
         <is>
-          <t>Liếm Cẩu Phản Diện Chỉ Nghĩ Cẩu , Nữ Chính Không Theo Sáo Lộ Đi [Convert]</t>
+          <t>Theo Nuốt Riêng Ngàn Vạn Ức Liếm Cẩu Kim Bắt Đầu Làm Thần Hào [Convert]</t>
         </is>
       </c>
       <c r="G976" t="inlineStr">
@@ -45310,11 +45310,11 @@
         </is>
       </c>
       <c r="I976" t="n">
-        <v>0.3907</v>
+        <v>0.3734</v>
       </c>
       <c r="J976" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/16145-liem-cau-phan-dien-chi-nghi-cau-nu-chinh-khong-theo-sao-lo-di-convert</t>
+          <t>https://sitruyencv.com/story/12662-theo-nuot-rieng-ngan-van-uc-liem-cau-kim-bat-dau-lam-than-hao-convert</t>
         </is>
       </c>
     </row>
@@ -45326,7 +45326,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C977" t="inlineStr">
@@ -45338,16 +45338,16 @@
         <v>6</v>
       </c>
       <c r="E977" t="n">
-        <v>19992</v>
+        <v>11756</v>
       </c>
       <c r="F977" t="inlineStr">
         <is>
-          <t>Trường Sinh Tu Tiên, Từ Thục Năng Sinh Xảo Bắt Đầu [Convert]</t>
+          <t>Ta Có Vô Hạn Tử Sĩ, Bạo Binh Quét Ngang Chư Thiên [Convert]</t>
         </is>
       </c>
       <c r="G977" t="inlineStr">
         <is>
-          <t>Tiên Hiệp</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H977" t="inlineStr">
@@ -45356,11 +45356,11 @@
         </is>
       </c>
       <c r="I977" t="n">
-        <v>0.3896</v>
+        <v>0.366</v>
       </c>
       <c r="J977" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/19992-truong-sinh-tu-tien-tu-thuc-nang-sinh-xao-bat-dau-convert</t>
+          <t>https://sitruyencv.com/story/11756-ta-co-vo-han-tu-si-bao-binh-quet-ngang-chu-thien-convert</t>
         </is>
       </c>
     </row>
@@ -45372,7 +45372,7 @@
       </c>
       <c r="B978" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C978" t="inlineStr">
@@ -45384,16 +45384,16 @@
         <v>7</v>
       </c>
       <c r="E978" t="n">
-        <v>17762</v>
+        <v>13094</v>
       </c>
       <c r="F978" t="inlineStr">
         <is>
-          <t>Ta Sáng Lập Siêu Phàm Thời Đại [Convert]</t>
+          <t>Tam Quốc: Ngôn Xuất Pháp Tùy, Tiệt Hồ Vớ Đen Hà Thái Hậu [Convert]</t>
         </is>
       </c>
       <c r="G978" t="inlineStr">
         <is>
-          <t>Khoa Huyễn</t>
+          <t>Dã Sử</t>
         </is>
       </c>
       <c r="H978" t="inlineStr">
@@ -45402,11 +45402,11 @@
         </is>
       </c>
       <c r="I978" t="n">
-        <v>0.3872</v>
+        <v>0.3641</v>
       </c>
       <c r="J978" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/17762-ta-sang-lap-sieu-pham-thoi-dai-convert</t>
+          <t>https://sitruyencv.com/story/13094-tam-quoc-ngon-xuat-phap-tuy-tiet-ho-vo-den-ha-thai-hau-convert</t>
         </is>
       </c>
     </row>
@@ -45418,7 +45418,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C979" t="inlineStr">
@@ -45430,29 +45430,29 @@
         <v>8</v>
       </c>
       <c r="E979" t="n">
-        <v>20776</v>
+        <v>10796</v>
       </c>
       <c r="F979" t="inlineStr">
         <is>
-          <t>Vạn Tộc Chiến Trường: Ta Có Hệ Thống Bạo Kích Hàng Tỷ Lần [Dịch]</t>
+          <t>Hoàng Đế Thế Thân: Ta Thể Chất Mỗi Ngày Gia Tăng Một Điểm [Convert]</t>
         </is>
       </c>
       <c r="G979" t="inlineStr">
         <is>
-          <t>Đô Thị, Võng Du, Hệ Thống</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H979" t="inlineStr">
         <is>
-          <t>Đang ra</t>
+          <t>Hoàn thành</t>
         </is>
       </c>
       <c r="I979" t="n">
-        <v>0.3846</v>
+        <v>0.3616</v>
       </c>
       <c r="J979" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/20776-van-toc-chien-truong-ta-co-he-thong-bao-kich-hang-ty-lan-dich</t>
+          <t>https://sitruyencv.com/story/10796-hoang-de-the-than-ta-the-chat-moi-ngay-gia-tang-mot-diem-convert</t>
         </is>
       </c>
     </row>
@@ -45464,7 +45464,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C980" t="inlineStr">
@@ -45476,16 +45476,16 @@
         <v>9</v>
       </c>
       <c r="E980" t="n">
-        <v>12225</v>
+        <v>13886</v>
       </c>
       <c r="F980" t="inlineStr">
         <is>
-          <t>Bắt Đầu Bị Quăng, Ta Quay Người Trở Thành Ức Vạn Phú Ông [Convert]</t>
+          <t>Độc Thủ Cứ Điểm Ba Năm, Ta Thành Đêm Dài Lãnh Chúa [Convert]</t>
         </is>
       </c>
       <c r="G980" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Khoa Huyễn</t>
         </is>
       </c>
       <c r="H980" t="inlineStr">
@@ -45494,11 +45494,11 @@
         </is>
       </c>
       <c r="I980" t="n">
-        <v>0.383</v>
+        <v>0.36</v>
       </c>
       <c r="J980" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/12225-bat-dau-bi-quang-ta-quay-nguoi-tro-thanh-uc-van-phu-ong-convert</t>
+          <t>https://sitruyencv.com/story/13886-doc-thu-cu-diem-ba-nam-ta-thanh-dem-dai-lanh-chua-convert</t>
         </is>
       </c>
     </row>
@@ -45510,7 +45510,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị</t>
+          <t>Tìm truyện xây dựng thế lực nhưng không có yếu tố đô thị và có nhiều hơn 300 chương</t>
         </is>
       </c>
       <c r="C981" t="inlineStr">
@@ -45522,16 +45522,16 @@
         <v>10</v>
       </c>
       <c r="E981" t="n">
-        <v>18919</v>
+        <v>18885</v>
       </c>
       <c r="F981" t="inlineStr">
         <is>
-          <t>Hoa Ngu: Sự Đản Sinh Của Một Đỉnh Lưu Mị Ma [Convert]</t>
+          <t>Chiến Thần Cuồng Tiêu Chi Chư Thiên Vạn Giới [Convert]</t>
         </is>
       </c>
       <c r="G981" t="inlineStr">
         <is>
-          <t>Đô Thị</t>
+          <t>Huyền Huyễn</t>
         </is>
       </c>
       <c r="H981" t="inlineStr">
@@ -45540,11 +45540,11 @@
         </is>
       </c>
       <c r="I981" t="n">
-        <v>0.3802</v>
+        <v>0.3589</v>
       </c>
       <c r="J981" t="inlineStr">
         <is>
-          <t>https://sitruyencv.com/story/18919-hoa-ngu-su-dan-sinh-cua-mot-dinh-luu-mi-ma-convert</t>
+          <t>https://sitruyencv.com/story/18885-chien-than-cuong-tieu-chi-chu-thien-van-gioi-convert</t>
         </is>
       </c>
     </row>
